--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -3128,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3153,68 +3153,68 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="152.5" customHeight="1">
+    <row r="2" ht="179.5" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>NO SCREEN EXISTS YET - NONE OF THESE CASES IS EXECUTABLE TODAY. SPM-46 so far delivers only the availability endpoint; the calendar screen (S-21) is not built. These cases were written against the acceptance criteria as the TARGET for that screen, so the page title, controls, column headings, cell labels and messages they name ('View availability', 'Show availability', 'Venue', 'From', 'To', 'Previous week', 'Next week', 'Free', 'Booked', 'Turnaround', 'Unavailable', 'Closed', 'Limited hours', 'Approved bookings', 'Unavailable periods', 'Room in use', 'Overlaps with') are the specification the screen will be built to, not an existing interface. Re-check the wording against the screen once it exists.</t>
+          <t>SCREEN BUILT, AND THESE CASES HAVE BEEN EXECUTED. When they were drafted the calendar screen (S-21) did not exist, and they were written against the acceptance criteria as its specification; the screen landed in the same commit. The wording they name ('View availability', 'Show availability', 'Venue', 'From', 'To', 'Previous week', 'Next week', 'Free', 'Booked', 'Turnaround', 'Unavailable', 'Closed', 'Limited hours', 'Approved bookings', 'Unavailable periods', 'Room in use', 'Overlaps with') was checked against src/app/venues/[id]/availability/page.tsx and matches. Executed 2026-09-26 against a running server, after merging main: 21 of the 22 pass and TC14 is not executable (see below). One wording note for TC11 - 'Classroom' is the screen's label for the stored value 'classroom' (layoutLabel(), page.tsx); the API itself carries the raw value.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
     </row>
-    <row r="3" ht="125.5" customHeight="1">
+    <row r="3" ht="206.5" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Team decision - how users reach the calendar: a 'View availability' link on every row of the Venues list, and a 'View availability' button on the venue edit page. The Venues list link is the one that matters for Event Coordinators, who hold the calendar permission but cannot open the edit page - their Venues list is read-only and its rows do not click - so a link on the edit page alone would have left the role this story most serves (identifying when venues may be requested, ahead of SPM-42) with no way in except typing the address. TC16 reaches the calendar through the Venues list link.</t>
+          <t>EVERY DATE IN THIS FILE ASSUMES A DATABASE SEEDED ON 2026-09-20 - RE-BASE THEM BEFORE RUNNING. prisma/seed.ts builds every date as day(n) = the day it was run + n days, so each date named under Preconditions and Test Data moves with every reseed, and a tester following the steps against a later seed sees an empty grid and reports a bug that isn't one. Add (your seed day - 2026-09-20) days to every date here. Your seed day is the date `npx prisma db seed` was last run; to recover it from the data instead, the Jurong Expo Floor renovation period always begins on seed day + 21. Measured on 2026-09-26 the offset was +6 days: 5 Oct -&gt; 11 Oct, 1 Oct -&gt; 7 Oct, 11-17 Oct -&gt; 17-23 Oct, 13 Oct -&gt; 19 Oct, 23 Oct -&gt; 29 Oct, 26 Oct -&gt; 1 Nov, 3 Nov -&gt; 9 Nov, 24 Nov -&gt; 30 Nov, 30 Nov -&gt; 6 Dec, 1 Dec -&gt; 7 Dec, 2 Dec -&gt; 8 Dec, 7 Dec -&gt; 13 Dec, 8 Dec -&gt; 14 Dec, 14 Dec -&gt; 20 Dec. Recorded as a Known Gap in DOCUMENTATION.md: it affects every story's test cases, not just this one, and the fix needs a team decision.</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
     </row>
-    <row r="4" ht="85" customHeight="1">
+    <row r="4" ht="125.5" customHeight="1">
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>AC5 cannot be tested by hand. Nothing in the app can create a venue unavailable period - the Block venue screen (S-23) is not built and nothing writes to that table - and the five seeded periods are at five different venues, so none overlap. TC14 needs two overlapping periods added to the demo data before it can run. Today AC5 is covered by unit tests only.</t>
+          <t>Team decision - how users reach the calendar: a 'View availability' link on every row of the Venues list, and a 'View availability' button on the venue edit page. The Venues list link is the one that matters for Event Coordinators, who hold the calendar permission but cannot open the edit page - their Venues list is read-only and its rows do not click - so a link on the edit page alone would have left the role this story most serves (identifying when venues may be requested, ahead of SPM-42) with no way in except typing the address. TC16 reaches the calendar through the Venues list link.</t>
         </is>
       </c>
       <c r="C4" s="11" t="n"/>
     </row>
-    <row r="5" ht="206.5" customHeight="1">
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Team decision - slot boundaries: AM 06:00–12:00, PM 12:00–18:00, Night 18:00–23:00, no slot crossing midnight, the same grid for every venue. SPM-46 names the three slots but never defines their times, and nothing else in the project does, so the team set them. A venue's own opening hours mark a slot closed or partly open but do not move the boundaries: a fixed grid keeps venues comparable, and nothing defines where PM would start if AM started at each venue's opening time. AM starts at 06:00 rather than the first-proposed 08:00 because 08:00 was measured against the demo data and was too late: of 13 approved bookings, four fell partly outside the grid once setup time was added - up to 120 minutes each - because Jurong Expo Floor opens at 06:00 and Marina Grand Hall's 180-minute setup puts a 09:00 event in the room from 06:00. With AM at 06:00 all 13 fit the grid, and the Sundara Hospitality Trade Showcase went from 120 minutes outside to 0. TC07 and every expected slot in TC08-TC13 and TC19 rest on these times.</t>
+          <t>AC5 cannot be tested by hand. Nothing in the app can create a venue unavailable period - the Block venue screen (S-23) is not built and nothing writes to that table - and the five seeded periods are at five different venues, so none overlap. TC14 needs two overlapping periods added to the demo data before it can run. Today AC5 is covered by unit tests only.</t>
         </is>
       </c>
       <c r="C5" s="11" t="n"/>
     </row>
-    <row r="6" ht="166" customHeight="1">
+    <row r="6" ht="206.5" customHeight="1">
       <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Team decision - 'confirmed bookings' in AC3 and AC7 means a booking whose own status is Approved, not a booking whose event is Confirmed. VenueBooking has no 'confirmed' status; Approved is the state that commits the room. The calendar exists to prevent double-booking, and the event-status reading was checked against the demo data and fails that: the Straits Medical Research Symposium booking at Marina Grand Hall on 1 Dec 2026 is approved while its event is still in Planning, so under the event-status reading the room would show as free and invite a second booking - discovered only at approval time, since this story blocks SPM-42. The event's status is still shown with each booking for information. TC19 is the case that proves this; TC20 and TC21 confirm pending, rejected and cancelled bookings do not block a slot.</t>
+          <t>Team decision - slot boundaries: AM 06:00–12:00, PM 12:00–18:00, Night 18:00–23:00, no slot crossing midnight, the same grid for every venue. SPM-46 names the three slots but never defines their times, and nothing else in the project does, so the team set them. A venue's own opening hours mark a slot closed or partly open but do not move the boundaries: a fixed grid keeps venues comparable, and nothing defines where PM would start if AM started at each venue's opening time. AM starts at 06:00 rather than the first-proposed 08:00 because 08:00 was measured against the demo data and was too late: of 13 approved bookings, four fell partly outside the grid once setup time was added - up to 120 minutes each - because Jurong Expo Floor opens at 06:00 and Marina Grand Hall's 180-minute setup puts a 09:00 event in the room from 06:00. With AM at 06:00 all 13 fit the grid, and the Sundara Hospitality Trade Showcase went from 120 minutes outside to 0. TC07 and every expected slot in TC08-TC13 and TC19 rest on these times.</t>
         </is>
       </c>
       <c r="C6" s="11" t="n"/>
     </row>
-    <row r="7" ht="58" customHeight="1">
+    <row r="7" ht="166" customHeight="1">
       <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Technical Support is internal staff, but cannot open the calendar (TC18) - the calendar reuses the venue catalogue's 'venue:view' permission, which Technical Support does not hold. AC6 says 'authorised internal users' without naming roles. Is excluding Technical Support intended?</t>
+          <t>Team decision - 'confirmed bookings' in AC3 and AC7 means a booking whose own status is Approved, not a booking whose event is Confirmed. VenueBooking has no 'confirmed' status; Approved is the state that commits the room. The calendar exists to prevent double-booking, and the event-status reading was checked against the demo data and fails that: the Straits Medical Research Symposium booking at Marina Grand Hall on 1 Dec 2026 is approved while its event is still in Planning, so under the event-status reading the room would show as free and invite a second booking - discovered only at approval time, since this story blocks SPM-42. The event's status is still shown with each booking for information. TC19 is the case that proves this; TC20 and TC21 confirm pending, rejected and cancelled bookings do not block a slot.</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
@@ -3225,29 +3225,29 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>What should a slot show when the room is open for only part of it? TC10 expects 'Free' with a 'Limited hours' note (One-North Rooftop Terrace opens at 16:00, so only 16:00–18:00 of PM is usable). The acceptance criteria do not cover opening hours at all.</t>
+          <t>Technical Support is internal staff, but cannot open the calendar (TC18) - the calendar reuses the venue catalogue's 'venue:view' permission, which Technical Support does not hold. AC6 says 'authorised internal users' without naming roles. Is excluding Technical Support intended?</t>
         </is>
       </c>
       <c r="C8" s="11" t="n"/>
     </row>
-    <row r="9" ht="85" customHeight="1">
+    <row r="9" ht="58" customHeight="1">
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>The S-21 mockup (design/mockups/VenueCalendar.dc.html) shows a continuous hour-by-hour grid, pending requests and 'tentative holds'. AC2 asks for AM/PM/Night slots, and the team chose to follow AC2. Pending requests are deliberately not shown (TC20), and 'tentative hold' does not exist anywhere in the data. Confirm the mockup is superseded for this screen.</t>
+          <t>What should a slot show when the room is open for only part of it? TC10 expects 'Free' with a 'Limited hours' note (One-North Rooftop Terrace opens at 16:00, so only 16:00–18:00 of PM is usable). The acceptance criteria do not cover opening hours at all.</t>
         </is>
       </c>
       <c r="C9" s="11" t="n"/>
     </row>
-    <row r="10" ht="58" customHeight="1">
+    <row r="10" ht="85" customHeight="1">
       <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>A booking whose room time falls outside every slot (between 23:00 and 06:00) would not appear in the grid at all. Nothing in the demo data does this today, so no case covers it. How should the screen warn about it?</t>
+          <t>The S-21 mockup (design/mockups/VenueCalendar.dc.html) shows a continuous hour-by-hour grid, pending requests and 'tentative holds'. AC2 asks for AM/PM/Night slots, and the team chose to follow AC2. Pending requests are deliberately not shown (TC20), and 'tentative hold' does not exist anywhere in the data. Confirm the mockup is superseded for this screen.</t>
         </is>
       </c>
       <c r="C10" s="11" t="n"/>
@@ -3258,10 +3258,21 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
+          <t>A booking whose room time falls outside every slot (between 23:00 and 06:00) would not appear in the grid at all. Nothing in the demo data does this today, so no case covers it. How should the screen warn about it?</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
           <t>Two checks the endpoint performs cannot be reached from a date picker and so have no test case: a date that does not exist (e.g. 31 Feb) and a date in the wrong format. The browser's date control cannot produce either.</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -1523,7 +1523,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-One-North Auditorium (ONE-AUD) has a 90-minute setup and an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 3 Nov 2026.
+One-North Auditorium (ONE-AUD) has a 90-minute setup and an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 9 Nov 2026.
 Logged in as Venue Staff.</t>
         </is>
       </c>
@@ -1551,8 +1551,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: One-North Auditorium (ONE-AUD)
-From: 3 Nov 2026
-To: 3 Nov 2026</t>
+From: 9 Nov 2026
+To: 9 Nov 2026</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
           <t>AM shows 'Free'.
 PM shows 'Turnaround' - the event starts at 18:00, but setup puts the room in use from 16:30.
 Night shows 'Booked' with 'Bayu Energy Transition Panel'.
-Under 'Approved bookings' the booking shows 3 Nov 2026, 18:00–21:00 and 'Room in use 16:30–22:00'.</t>
+Under 'Approved bookings' the booking shows 9 Nov 2026, 18:00–21:00 and 'Room in use 16:30–22:00'.</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Jurong Expo Floor (JUR-EXP) has a 240-minute setup and 180-minute teardown, and an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 24 Nov 2026.
+Jurong Expo Floor (JUR-EXP) has a 240-minute setup and 180-minute teardown, and an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 30 Nov 2026.
 Logged in as Venue Staff.</t>
         </is>
       </c>
@@ -1717,8 +1717,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 24 Nov 2026
-To: 24 Nov 2026</t>
+From: 30 Nov 2026
+To: 30 Nov 2026</t>
         </is>
       </c>
     </row>
@@ -1882,8 +1882,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: One-North Rooftop Terrace (ONE-ROOF)
-From: 5 Oct 2026
-To: 5 Oct 2026</t>
+From: 11 Oct 2026
+To: 11 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Jurong Training Room (JUR-TRN) has an approved booking, 'Harbourline Claims Systems Training', 09:00–17:00 on 13 Oct 2026, whose event is confirmed.
+Jurong Training Room (JUR-TRN) has an approved booking, 'Harbourline Claims Systems Training', 09:00–17:00 on 19 Oct 2026, whose event is confirmed.
 Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
         </is>
       </c>
@@ -2047,8 +2047,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Training Room (JUR-TRN)
-From: 13 Oct 2026
-To: 13 Oct 2026</t>
+From: 19 Oct 2026
+To: 19 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>AM and PM show 'Booked' with 'Harbourline Claims Systems Training'.
-Under 'Approved bookings' the booking is listed with the event status 'Confirmed', 13 Oct 2026, 09:00–17:00, layout 'Classroom'.</t>
+Under 'Approved bookings' the booking is listed with the event status 'Confirmed', 19 Oct 2026, 09:00–17:00, layout 'Classroom'.</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Jurong Expo Floor (JUR-EXP) is recorded as unavailable for renovation from 11 Oct 2026 to 18 Oct 2026.
+Jurong Expo Floor (JUR-EXP) is recorded as unavailable for renovation from 17 Oct 2026 to 24 Oct 2026.
 Logged in as Venue Staff.</t>
         </is>
       </c>
@@ -2211,8 +2211,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 11 Oct 2026
-To: 17 Oct 2026</t>
+From: 17 Oct 2026
+To: 23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -2224,8 +2224,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Every slot on every day from 11 to 17 Oct 2026 shows 'Unavailable'.
-Under 'Unavailable periods' one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 11 Oct 2026 to 18 Oct 2026.</t>
+          <t>Every slot on every day from 17 to 23 Oct 2026 shows 'Unavailable'.
+Under 'Unavailable periods' one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Marina Boardroom 2 (MAR-BR2) is recorded as unavailable for renovation from 19 Nov 2026 to 3 Dec 2026, ending 23:59 on 3 Dec.
+Marina Boardroom 2 (MAR-BR2) is recorded as unavailable for renovation from 25 Nov 2026 to 9 Dec 2026, ending 23:59 on 9 Dec.
 Logged in as Venue Staff.</t>
         </is>
       </c>
@@ -2375,8 +2375,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Marina Boardroom 2 (MAR-BR2)
-From: 1 Dec 2026
-To: 7 Dec 2026</t>
+From: 7 Dec 2026
+To: 13 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -2388,9 +2388,9 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Every slot on 1, 2 and 3 Dec 2026 shows 'Unavailable'.
-Every slot from 4 to 7 Dec 2026 shows 'Free'.
-'Unavailable periods' lists the period as 'Refurbishment of the boardroom fit-out.', 19 Nov to 3 Dec 2026.</t>
+          <t>Every slot on 7, 8 and 9 Dec 2026 shows 'Unavailable'.
+Every slot from 10 to 13 Dec 2026 shows 'Free'.
+'Unavailable periods' lists the period as 'Refurbishment of the boardroom fit-out.', 25 Nov to 9 Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -2540,10 +2540,10 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-Period A: 12 Oct 2026 08:00–14:00, maintenance
-Period B: 12 Oct 2026 12:00–18:00, safety
-From: 12 Oct 2026
-To: 12 Oct 2026</t>
+Period A: 18 Oct 2026 08:00–14:00, maintenance
+Period B: 18 Oct 2026 12:00–18:00, safety
+From: 18 Oct 2026
+To: 18 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Jurong Expo Floor (JUR-EXP) has one unavailable period, 11-18 Oct 2026, and no bookings in that week.
+Jurong Expo Floor (JUR-EXP) has one unavailable period, 17-24 Oct 2026, and no bookings in that week.
 Logged in as Venue Staff.</t>
         </is>
       </c>
@@ -2706,8 +2706,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 11 Oct 2026
-To: 17 Oct 2026</t>
+From: 17 Oct 2026
+To: 23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3164,13 +3164,13 @@
       </c>
       <c r="C2" s="11" t="n"/>
     </row>
-    <row r="3" ht="206.5" customHeight="1">
+    <row r="3" ht="287.5" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>EVERY DATE IN THIS FILE ASSUMES A DATABASE SEEDED ON 2026-09-20 - RE-BASE THEM BEFORE RUNNING. prisma/seed.ts builds every date as day(n) = the day it was run + n days, so each date named under Preconditions and Test Data moves with every reseed, and a tester following the steps against a later seed sees an empty grid and reports a bug that isn't one. Add (your seed day - 2026-09-20) days to every date here. Your seed day is the date `npx prisma db seed` was last run; to recover it from the data instead, the Jurong Expo Floor renovation period always begins on seed day + 21. Measured on 2026-09-26 the offset was +6 days: 5 Oct -&gt; 11 Oct, 1 Oct -&gt; 7 Oct, 11-17 Oct -&gt; 17-23 Oct, 13 Oct -&gt; 19 Oct, 23 Oct -&gt; 29 Oct, 26 Oct -&gt; 1 Nov, 3 Nov -&gt; 9 Nov, 24 Nov -&gt; 30 Nov, 30 Nov -&gt; 6 Dec, 1 Dec -&gt; 7 Dec, 2 Dec -&gt; 8 Dec, 7 Dec -&gt; 13 Dec, 8 Dec -&gt; 14 Dec, 14 Dec -&gt; 20 Dec. Recorded as a Known Gap in DOCUMENTATION.md: it affects every story's test cases, not just this one, and the fix needs a team decision.</t>
+          <t>DATES IN THIS FILE MATCH A DATABASE SEEDED ON 2026-09-26. RE-BASE THEM IF YOURS WAS SEEDED ON ANOTHER DAY. prisma/seed.ts builds every date as day(n) = the day it was run + n days, so every date under Preconditions, Test Data and Expected Result moves with each reseed; a tester on a different seed follows the steps, sees an empty grid, and reports a bug that isn't one. These cases were first written against a 2026-09-20 seed and were re-based +6 days on 2026-09-26, then verified case by case against a running server. To re-base again, add (your seed day - 2026-09-26) days to every date. Your seed day is the date `npx prisma db seed` was last run; to recover it from the data instead, the Jurong Expo Floor renovation period always begins on seed day + 21. Every fixture these cases use sits at a fixed offset in prisma/seed.ts, so the dates can also be rebuilt from the seed day directly: Rooftop Terrace free day = +15; Jurong Expo Floor renovation = +21 to +28; Harbourline Claims training = +23; Changi Meeting Room 2 cancelled booking = +33; Marina Auditorium rejected booking = +36; Bayu Energy panel = +44; Marina Boardroom 2 refurbishment = +60 to +74; Sundara Trade Showcase = +65; Straits Medical Symposium = +72; Pearl Delta pending request = +79; Meridian Wealth Forum = +85. Recorded as a Known Gap in DOCUMENTATION.md: it affects every story's test cases, not just this one, and a permanent fix needs a team decision.</t>
         </is>
       </c>
       <c r="C3" s="11" t="n"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Team decision - 'confirmed bookings' in AC3 and AC7 means a booking whose own status is Approved, not a booking whose event is Confirmed. VenueBooking has no 'confirmed' status; Approved is the state that commits the room. The calendar exists to prevent double-booking, and the event-status reading was checked against the demo data and fails that: the Straits Medical Research Symposium booking at Marina Grand Hall on 1 Dec 2026 is approved while its event is still in Planning, so under the event-status reading the room would show as free and invite a second booking - discovered only at approval time, since this story blocks SPM-42. The event's status is still shown with each booking for information. TC19 is the case that proves this; TC20 and TC21 confirm pending, rejected and cancelled bookings do not block a slot.</t>
+          <t>Team decision - 'confirmed bookings' in AC3 and AC7 means a booking whose own status is Approved, not a booking whose event is Confirmed. VenueBooking has no 'confirmed' status; Approved is the state that commits the room. The calendar exists to prevent double-booking, and the event-status reading was checked against the demo data and fails that: the Straits Medical Research Symposium booking at Marina Grand Hall on 7 Dec 2026 is approved while its event is still in Planning, so under the event-status reading the room would show as free and invite a second booking - discovered only at approval time, since this story blocks SPM-42. The event's status is still shown with each booking for information. TC19 is the case that proves this; TC20 and TC21 confirm pending, rejected and cancelled bookings do not block a slot.</t>
         </is>
       </c>
       <c r="C7" s="11" t="n"/>
@@ -3481,7 +3481,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Marina Grand Hall (MAR-GH) has an APPROVED booking, 'Straits Medical Research Symposium', 09:00–18:00 on 1 Dec 2026, whose EVENT is still in Planning - not Confirmed.
+Marina Grand Hall (MAR-GH) has an APPROVED booking, 'Straits Medical Research Symposium', 09:00–18:00 on 7 Dec 2026, whose EVENT is still in Planning - not Confirmed.
 Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
         </is>
       </c>
@@ -3509,8 +3509,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Marina Grand Hall (MAR-GH)
-From: 1 Dec 2026
-To: 1 Dec 2026</t>
+From: 7 Dec 2026
+To: 7 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Changi Conference Centre (CBP-CONF) has a PENDING booking request, 'Pearl Delta Safety Conference', on 8 Dec 2026, and no approved booking that day.
+Changi Conference Centre (CBP-CONF) has a PENDING booking request, 'Pearl Delta Safety Conference', on 14 Dec 2026, and no approved booking that day.
 Logged in as Event Coordinator.</t>
         </is>
       </c>
@@ -3675,8 +3675,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Changi Conference Centre (CBP-CONF)
-From: 8 Dec 2026
-To: 8 Dec 2026</t>
+From: 14 Dec 2026
+To: 14 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -3811,8 +3811,8 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Marina Auditorium (MAR-AUD) has a REJECTED booking for 'Nusantara Developer Summit' on 26 Oct 2026.
-Changi Meeting Room 2 (CBP-MTG2) has a CANCELLED booking for 'Pearl Delta Supplier Forum' on 23 Oct 2026.
+Marina Auditorium (MAR-AUD) has a REJECTED booking for 'Nusantara Developer Summit' on 1 Nov 2026.
+Changi Meeting Room 2 (CBP-MTG2) has a CANCELLED booking for 'Pearl Delta Supplier Forum' on 29 Oct 2026.
 Logged in as Event Coordinator.</t>
         </is>
       </c>
@@ -3840,8 +3840,8 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Marina Auditorium (MAR-AUD): 26 Oct 2026
-Changi Meeting Room 2 (CBP-MTG2): 23 Oct 2026</t>
+          <t>Marina Auditorium (MAR-AUD): 1 Nov 2026
+Changi Meeting Room 2 (CBP-MTG2): 29 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3853,8 +3853,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Every slot at Marina Auditorium on 26 Oct 2026 shows 'Free', and 'Nusantara Developer Summit' is not listed.
-Every slot at Changi Meeting Room 2 on 23 Oct 2026 shows 'Free', and 'Pearl Delta Supplier Forum' is not listed.</t>
+          <t>Every slot at Marina Auditorium on 1 Nov 2026 shows 'Free', and 'Nusantara Developer Summit' is not listed.
+Every slot at Changi Meeting Room 2 on 29 Oct 2026 shows 'Free', and 'Pearl Delta Supplier Forum' is not listed.</t>
         </is>
       </c>
     </row>
@@ -4006,8 +4006,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Skills Lab (JUR-LAB)
-From: 1 Dec 2026
-To: 7 Dec 2026</t>
+From: 7 Dec 2026
+To: 13 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -4171,8 +4171,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Marina Grand Hall (MAR-GH)
-From: 1 Dec 2026
-To: 7 Dec 2026</t>
+From: 7 Dec 2026
+To: 13 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>The 'Marina Grand Hall availability' page opens.
-The grid shows exactly seven day rows, 1 Dec 2026 to 7 Dec 2026, each with AM, PM and Night columns.
+The grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026, each with AM, PM and Night columns.
 The 'Venue' picker shows Marina Grand Hall.</t>
         </is>
       </c>
@@ -4469,7 +4469,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data freshly loaded.
-Logged in as Venue Staff and viewing Marina Grand Hall's availability for 24-30 Nov 2026.</t>
+Logged in as Venue Staff and viewing Marina Grand Hall's availability for 30 Nov 2026 to 6 Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -4495,8 +4495,8 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 24 Nov 2026
-To: 30 Nov 2026</t>
+From: 30 Nov 2026
+To: 6 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -4509,8 +4509,8 @@
       <c r="B6" s="13" t="inlineStr">
         <is>
           <t>The page title changes to 'Jurong Expo Floor availability'.
-The row for 24 Nov 2026 shows the 'Sundara Hospitality Trade Showcase' booking.
-The date range stays 24-30 Nov 2026.</t>
+The row for 30 Nov 2026 shows the 'Sundara Hospitality Trade Showcase' booking.
+The date range stays 30 Nov 2026 to 6 Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -4657,8 +4657,8 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>From: 5 Oct 2026
-To: 1 Oct 2026</t>
+          <t>From: 11 Oct 2026
+To: 7 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4819,9 +4819,9 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>From: 1 Oct 2026
-62 days - To: 1 Dec 2026
-63 days - To: 2 Dec 2026</t>
+          <t>From: 7 Oct 2026
+62 days - To: 7 Dec 2026
+63 days - To: 8 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -4833,8 +4833,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>With To = 1 Dec 2026, the grid shows 62 day rows, 1 Oct to 1 Dec 2026.
-With To = 2 Dec 2026, the message 'Choose a range of 62 days or fewer - this one is 63.' is shown and no grid is shown.</t>
+          <t>With To = 7 Dec 2026, the grid shows 62 day rows, 7 Oct to 7 Dec 2026.
+With To = 8 Dec 2026, the message 'Choose a range of 62 days or fewer - this one is 63.' is shown and no grid is shown.</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Venue Staff and viewing Marina Grand Hall's availability for 1-7 Dec 2026.</t>
+          <t>Logged in as Venue Staff and viewing Marina Grand Hall's availability for 7-13 Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -4980,11 +4980,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Starting range: 1 Dec 2026 - 7 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>Starting range: 7 Dec 2026 - 13 Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4992,8 +4992,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>After 'Next week' the grid shows 8-14 Dec 2026, and the 14 Dec row shows the 'Meridian Wealth Management Forum' booking.
-After 'Previous week' twice the grid shows 24-30 Nov 2026.</t>
+          <t>After 'Next week' the grid shows 14-20 Dec 2026, and the 20 Dec row shows the 'Meridian Wealth Management Forum' booking.
+After 'Previous week' twice the grid shows 30 Nov 2026 to 6 Dec 2026.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -7,29 +7,21 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Open Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TC01" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TC02" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TC03" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TC04" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TC05" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TC06" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="TC07" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TC08" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="TC09" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="TC10" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TC11" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="TC12" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="TC13" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="TC14" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="TC15" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="TC16" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="TC17" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="TC18" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="TC19" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="TC20" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="TC21" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="TC22" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="TC01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TC02" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TC03" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TC04" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TC05" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC06" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TC07" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TC08" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TC09" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TC10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TC11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TC13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TC14" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TC15" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -469,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -541,12 +533,12 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Venue Staff open a venue's availability for a chosen date range</t>
+          <t>Open a venue's availability and read the grid</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>AC1, AC2</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -573,7 +565,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>With no dates chosen, the page shows a week from today</t>
+          <t>An end date before the start date is rejected</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -583,12 +575,12 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -605,7 +597,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Choosing a different venue shows that venue's availability</t>
+          <t>A range of 62 days is accepted and 63 days is rejected</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -615,7 +607,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -637,7 +629,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>An end date before the start date is rejected</t>
+          <t>Previous week and Next week move the range by seven days</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -647,12 +639,12 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -669,22 +661,22 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>A range of 62 days is accepted and 63 days is rejected</t>
+          <t>Setup time puts the room in use before the event, in the earlier slot</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>AC2</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -701,12 +693,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Previous week and Next week move the range by seven days</t>
+          <t>Teardown keeps the room in use after the event, into the later slot</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>AC1</t>
+          <t>AC2</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -716,7 +708,7 @@
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -733,7 +725,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Each day is split into the three fixed slots</t>
+          <t>A venue's opening hours mark slots Closed or Limited hours</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -765,12 +757,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>A slot taken only by setup time shows as Turnaround</t>
+          <t>A recorded unavailable period covers every slot it spans</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>AC2</t>
+          <t>AC4</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -797,17 +789,17 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Teardown after an event pushes it into the next slot</t>
+          <t>A multi-day unavailable period stops on its last day</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>AC2</t>
+          <t>AC4</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -829,22 +821,22 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>A venue's opening hours mark slots closed or limited</t>
+          <t>Two overlapping unavailable periods are identified as overlapping</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>AC2</t>
+          <t>AC5</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
@@ -861,12 +853,12 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>An approved booking is shown with its event and times</t>
+          <t>An Event Coordinator and an Operations Manager can open the calendar</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC6</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -893,17 +885,17 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>A recorded unavailable period is shown on every slot it covers</t>
+          <t>A role without venue permissions cannot open the calendar</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>AC4</t>
+          <t>AC6</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -925,17 +917,17 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>A multi-day unavailable period stops on its last day</t>
+          <t>An approved booking blocks its slots, and is listed, even while its event is still in planning</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>AC4</t>
+          <t>AC3, AC7</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -957,17 +949,17 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Two overlapping unavailable periods are identified as overlapping</t>
+          <t>Pending, rejected and cancelled bookings never block a slot</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -989,12 +981,12 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>A single unavailable period is not reported as overlapping</t>
+          <t>A retired venue's slots are never offered as free</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1004,417 +996,187 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>TC16</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC16</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>An Event Coordinator can open the availability calendar</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>AC6</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>TC17</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC17</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>An Event Organiser cannot open the availability calendar</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>AC6</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>TC18</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC18</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Technical Support staff cannot open the availability calendar</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>AC6</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>TC19</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Acceptance Criterion</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Covered by</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>AC1</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>SPM-46-TC19</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>An approved booking blocks its slots even while its event is still in planning</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>AC7, AC3</t>
-        </is>
-      </c>
+          <t>Users can select a venue and date/time period.</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
       <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>TC20</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC20</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>A pending booking request does not block a slot</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>TC21</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC21</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Rejected and cancelled bookings do not block a slot</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>TC22</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC22</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>A retired venue's empty slots are never offered as free</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Acceptance Criterion</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Covered by</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="85" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Users can select a venue and date/time period.</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>SPM-46-TC01
 SPM-46-TC02
 SPM-46-TC03
-SPM-46-TC04
+SPM-46-TC04</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>AC2</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Availability is shown per fixed slot (AM, PM, Night) for each day, including slots occupied by setup or turnaround time.</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>SPM-46-TC01
 SPM-46-TC05
-SPM-46-TC06</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="n"/>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>AC2</t>
+SPM-46-TC06
+SPM-46-TC07</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>AC3</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Existing confirmed bookings are displayed.</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>SPM-46-TC13</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n"/>
+    </row>
+    <row r="25" ht="31" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>AC4</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Recorded unavailable periods are displayed.</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>SPM-46-TC08
+SPM-46-TC09</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>AC5</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Overlapping unavailable periods are identifiable.</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>SPM-46-TC10</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="31" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Only authorised internal users can access the availability calendar.</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>SPM-46-TC11
+SPM-46-TC12</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="44.5" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>AC7</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Availability reflects confirmed bookings.</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>SPM-46-TC13
+SPM-46-TC14
+SPM-46-TC15</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n"/>
+    </row>
+    <row r="30" ht="125.5" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Code reviewed</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Availability is shown per fixed slot (AM, PM, Night) for each day, including slots occupied by setup or turnaround time.</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC07
-SPM-46-TC08
-SPM-46-TC09
-SPM-46-TC10</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="31" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>AC3</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Existing confirmed bookings are displayed.</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC11
-SPM-46-TC19</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="31" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>AC4</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Recorded unavailable periods are displayed.</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC12
-SPM-46-TC13</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="n"/>
-    </row>
-    <row r="33" ht="31" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>AC5</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Overlapping unavailable periods are identifiable.</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC14
-SPM-46-TC15</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="n"/>
-    </row>
-    <row r="34" ht="44.5" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>AC6</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Only authorised internal users can access the availability calendar.</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC16
-SPM-46-TC17
-SPM-46-TC18</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="n"/>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Availability reflects confirmed bookings.</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC19
-SPM-46-TC20
-SPM-46-TC21
-SPM-46-TC22</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="n"/>
-    </row>
-    <row r="37" ht="125.5" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Code reviewed</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>src/app/api/venues/[id]/availability/route.ts
 src/lib/venueAvailability.ts
@@ -1427,31 +1189,31 @@
 design/mockups/VenueCalendar.dc.html</t>
         </is>
       </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="9" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B1:F1"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1469,13 +1231,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1510,11 +1265,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC08</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
+          <t>SPM-46-TC09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1522,9 +1277,9 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-One-North Auditorium (ONE-AUD) has a 90-minute setup and an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 9 Nov 2026.
-Logged in as Venue Staff.</t>
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Marina Boardroom 2 (MAR-BR2) is recorded as unavailable for renovation from 25 Nov 2026 to 9 Dec 2026, ending 23:59 on 9 Dec.
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
@@ -1536,8 +1291,8 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for One-North Auditorium
-2. Set 'From' and 'To' to the same date
+          <t>1. Open the availability page for Marina Boardroom 2
+2. Set 'From' to 7 Dec 2026 and 'To' to 13 Dec 2026
 3. Click 'Show availability'</t>
         </is>
       </c>
@@ -1550,13 +1305,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: One-North Auditorium (ONE-AUD)
-From: 9 Nov 2026
-To: 9 Nov 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
+          <t>Venue: Marina Boardroom 2 (MAR-BR2)
+From: 7 Dec 2026
+To: 13 Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1564,10 +1319,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM shows 'Free'.
-PM shows 'Turnaround' - the event starts at 18:00, but setup puts the room in use from 16:30.
-Night shows 'Booked' with 'Bayu Energy Transition Panel'.
-Under 'Approved bookings' the booking shows 9 Nov 2026, 18:00–21:00 and 'Room in use 16:30–22:00'.</t>
+          <t>Every slot on 7, 8 and 9 Dec 2026 shows 'Unavailable'. Every slot from 10 to 13 Dec 2026 shows 'Free' — the period stops on its last day and does not spill into 10 Dec. 'Unavailable periods' lists it as 'Refurbishment of the boardroom fit-out.', 25 Nov to 9 Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1342,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -1676,11 +1428,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
+          <t>SPM-46-TC10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="139" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1688,9 +1440,8 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-Jurong Expo Floor (JUR-EXP) has a 240-minute setup and 180-minute teardown, and an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 30 Nov 2026.
-Logged in as Venue Staff.</t>
+          <t>BLOCKED — NOT RUNNABLE ON THE DEMO DATA. Nothing in the app can create a venue unavailable period: the Block venue screen (S-23) is not built and no route writes to that table, and the five seeded periods sit at five different venues, so none overlap. Two overlapping periods must be added to prisma/seed.ts before this can run. The rule itself is covered by the unit tests in src/lib/__tests__/venueAvailability.test.ts. Recorded under Known Gaps in DOCUMENTATION.md.
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1454,12 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' and 'To' to the same date
+2. Set 'From' and 'To' to cover both periods
 3. Click 'Show availability'</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="44.5" customHeight="1">
+    <row r="5" ht="71.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1717,12 +1468,14 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 30 Nov 2026
-To: 30 Nov 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+Period A: 18 Oct 2026 08:00–14:00, maintenance
+Period B: 18 Oct 2026 12:00–18:00, safety
+From: 18 Oct 2026
+To: 18 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1730,9 +1483,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM shows 'Booked' and PM shows 'Booked', each with 'Sundara Hospitality Trade Showcase'.
-Night shows 'Turnaround' - the event ends at 18:00, but teardown keeps the room in use until 21:00.
-The booking shows 'Room in use 06:00–21:00'.</t>
+          <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid, and under 'Unavailable periods' each of the two periods is marked 'Overlaps with' the other.</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1506,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -1841,11 +1592,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
+          <t>SPM-46-TC11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1853,13 +1604,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-One-North Rooftop Terrace (ONE-ROOF) is open 16:00–23:00 only.
-Logged in as Venue Staff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1867,9 +1616,10 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for One-North Rooftop Terrace
-2. Set 'From' and 'To' to a date with no bookings
-3. Click 'Show availability'</t>
+          <t>1. Click 'Venues' in the sidebar
+2. On the 'Marina Grand Hall' row, click 'View availability'
+3. Go back to 'Venues' and click elsewhere on the 'Marina Grand Hall' row
+4. Sign out, sign in as the Operations Manager, and repeat the first two steps</t>
         </is>
       </c>
     </row>
@@ -1881,13 +1631,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: One-North Rooftop Terrace (ONE-ROOF)
-From: 11 Oct 2026
-To: 11 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Accounts: daniel.tan@connectsphere.com (Event Coordinator), grace.lim@connectsphere.com (Operations Manager)
+Venue: Marina Grand Hall (MAR-GH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1895,9 +1644,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM shows 'Closed' - the terrace is shut for the whole of 06:00–12:00.
-PM shows 'Free' with the note 'Limited hours' - it is open only from 16:00.
-Night shows 'Free' with no note.</t>
+          <t>The 'Marina Grand Hall availability' page opens and shows the grid for both accounts. Clicking elsewhere on the row does nothing — the Venues list stays read-only for a coordinator.</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1667,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -2006,11 +1753,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="85" customHeight="1">
+          <t>SPM-46-TC12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2018,13 +1765,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-Jurong Training Room (JUR-TRN) has an approved booking, 'Harbourline Claims Systems Training', 09:00–17:00 on 19 Oct 2026, whose event is confirmed.
-Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>The tester knows the availability page address for Marina Grand Hall.
+Accounts available: rachel.ng@meridianfina.com (Event Organiser) and kenji.sato@connectsphere.com (Technical Support), both / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2032,13 +1778,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Jurong Training Room
-2. Set 'From' and 'To' to the same date
-3. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Sign in as the Event Organiser and confirm 'Venues' is not in the sidebar
+2. Paste the Marina Grand Hall availability page address into the address bar and press Enter
+3. Sign out, sign in as Technical Support, and open the same address</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2046,9 +1792,8 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Jurong Training Room (JUR-TRN)
-From: 19 Oct 2026
-To: 19 Oct 2026</t>
+          <t>Account: rachel.ng@meridianfina.com (Event Organiser)
+Account: kenji.sato@connectsphere.com (Technical Support)</t>
         </is>
       </c>
     </row>
@@ -2060,8 +1805,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM and PM show 'Booked' with 'Harbourline Claims Systems Training'.
-Under 'Approved bookings' the booking is listed with the event status 'Confirmed', 19 Oct 2026, 09:00–17:00, layout 'Classroom'.</t>
+          <t>For both accounts the page shows 'Venue availability is for ConnectSphere staff'. No grid, no bookings and no unavailable periods are shown. Technical Support is internal staff but still has no access, because the calendar reuses the venue catalogue's permission.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +1828,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -2170,11 +1914,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC12</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
+          <t>SPM-46-TC13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2182,13 +1926,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-Jurong Expo Floor (JUR-EXP) is recorded as unavailable for renovation from 17 Oct 2026 to 24 Oct 2026.
-Logged in as Venue Staff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Marina Grand Hall (MAR-GH) has an APPROVED booking, 'Straits Medical Research Symposium', 09:00–18:00 on 7 Dec 2026, whose EVENT is still in Planning — not Confirmed. The venue has a 180-minute setup and 120-minute teardown.
+Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2196,9 +1940,10 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' and 'To'
-3. Click 'Show availability'</t>
+          <t>1. Open the availability page for Marina Grand Hall
+2. Set 'From' and 'To' to the same date
+3. Click 'Show availability'
+4. Read the booking under 'Approved bookings'</t>
         </is>
       </c>
     </row>
@@ -2210,13 +1955,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 17 Oct 2026
-To: 23 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Venue: Marina Grand Hall (MAR-GH)
+From: 7 Dec 2026
+To: 7 Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2224,8 +1969,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Every slot on every day from 17 to 23 Oct 2026 shows 'Unavailable'.
-Under 'Unavailable periods' one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026.</t>
+          <t>AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free'. Night shows 'Turnaround' (teardown to 20:00). Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use 06:00–20:00'. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
         </is>
       </c>
     </row>
@@ -2248,7 +1992,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -2334,11 +2078,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
+          <t>SPM-46-TC14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="152.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2346,13 +2090,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-Marina Boardroom 2 (MAR-BR2) is recorded as unavailable for renovation from 25 Nov 2026 to 9 Dec 2026, ending 23:59 on 9 Dec.
-Logged in as Venue Staff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Changi Conference Centre (CBP-CONF) has a PENDING booking request, 'Pearl Delta Safety Conference', on 14 Dec 2026 and no approved booking that day. Marina Auditorium (MAR-AUD) has a REJECTED booking for 'Nusantara Developer Summit' on 1 Nov 2026. Changi Meeting Room 2 (CBP-MTG2) has a CANCELLED booking for 'Pearl Delta Supplier Forum' on 29 Oct 2026.
+Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2360,9 +2104,9 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Marina Boardroom 2
-2. Set 'From' and 'To'
-3. Click 'Show availability'</t>
+          <t>1. Open the availability page for Changi Conference Centre for 14 Dec 2026
+2. Choose Marina Auditorium from the 'Venue' picker and show 1 Nov 2026
+3. Choose Changi Meeting Room 2 from the 'Venue' picker and show 29 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -2374,9 +2118,9 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Marina Boardroom 2 (MAR-BR2)
-From: 7 Dec 2026
-To: 13 Dec 2026</t>
+          <t>Changi Conference Centre (CBP-CONF): 14 Dec 2026
+Marina Auditorium (MAR-AUD): 1 Nov 2026
+Changi Meeting Room 2 (CBP-MTG2): 29 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -2388,9 +2132,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Every slot on 7, 8 and 9 Dec 2026 shows 'Unavailable'.
-Every slot from 10 to 13 Dec 2026 shows 'Free'.
-'Unavailable periods' lists the period as 'Refurbishment of the boardroom fit-out.', 25 Nov to 9 Dec 2026.</t>
+          <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2155,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -2499,11 +2241,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="98.5" customHeight="1">
+          <t>SPM-46-TC15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2511,13 +2253,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>NOT RUNNABLE ON THE CURRENT DEMO DATA - see Open Questions.
-Jurong Expo Floor (JUR-EXP) must have two overlapping unavailable periods recorded. The app has no way to create one (the Block venue screen, S-23, is not built) and the seeded periods never overlap, so these must be added to the demo data first.
-Logged in as Venue Staff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Jurong Skills Lab (JUR-LAB) is active and has no bookings.
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2525,13 +2267,15 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' and 'To' to cover both periods
-3. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.5" customHeight="1">
+          <t>1. Open Jurong Skills Lab from the Venues list
+2. Click 'Retire venue', then 'Retire venue' in the confirmation dialog
+3. Click 'View availability'
+4. Set 'From' to 7 Dec 2026 and 'To' to 13 Dec 2026, then click 'Show availability'
+5. Return to the venue and click 'Restore venue' to undo the retirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2539,15 +2283,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Jurong Expo Floor (JUR-EXP)
-Period A: 18 Oct 2026 08:00–14:00, maintenance
-Period B: 18 Oct 2026 12:00–18:00, safety
-From: 18 Oct 2026
-To: 18 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>Venue: Jurong Skills Lab (JUR-LAB)
+From: 7 Dec 2026
+To: 13 Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2555,8 +2297,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid.
-Under 'Unavailable periods' each of the two periods is marked 'Overlaps with' the other.</t>
+          <t>The availability page shows the warning 'This venue is retired'. Every slot on every day shows 'Closed' — none shows 'Free'. After 'Restore venue' the venue is active again.</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2320,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -2636,7 +2377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2665,11 +2406,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
+          <t>SPM-46-TC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2677,13 +2418,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-Jurong Expo Floor (JUR-EXP) has one unavailable period, 17-24 Oct 2026, and no bookings in that week.
-Logged in as Venue Staff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2691,13 +2431,17 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' and 'To'
-3. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Click 'Venues' in the sidebar
+2. On the 'Marina Grand Hall' row, click 'View availability'
+3. Read the range the page opens with, and the three column headings
+4. Set 'From' to 7 Dec 2026 and 'To' to 13 Dec 2026
+5. Click 'Show availability'
+6. Choose 'Jurong Expo Floor' from the 'Venue' picker
+7. Click 'Show availability'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2705,13 +2449,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 17 Oct 2026
-To: 23 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>Venue: Marina Grand Hall (MAR-GH), then Jurong Expo Floor (JUR-EXP)
+From: 7 Dec 2026
+To: 13 Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="152.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2719,8 +2463,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>No overlap warning is shown.
-The period under 'Unavailable periods' has no 'Overlaps with' note.</t>
+          <t>The 'Marina Grand Hall availability' page opens on a week from today (Singapore time): seven day rows, with 'From' and 'To' already filled in with those two dates. The grid has exactly three columns, in this order, each showing its times: AM 06:00–12:00, PM 12:00–18:00, Night 18:00–23:00. After 'Show availability' the grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026 (the 7 Dec row is not empty — it carries the Straits Medical Research Symposium booking). Choosing Jurong Expo Floor changes the title to 'Jurong Expo Floor availability', keeps the range at 7–13 Dec 2026, and shows the same three columns.</t>
         </is>
       </c>
     </row>
@@ -2743,1307 +2486,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC16</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Click 'Venues' in the sidebar
-2. On the 'Marina Grand Hall' row, click 'View availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Account: daniel.tan@connectsphere.com (Event Coordinator)
-Venue: Marina Grand Hall (MAR-GH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>The 'Marina Grand Hall availability' page opens and shows the grid.
-Clicking elsewhere on the row does nothing - the Venues list stays read-only for a coordinator.
-The same link works for grace.lim@connectsphere.com (Operations Manager).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Logged in as an Event Organiser: rachel.ng@meridianfina.com / password123
-The tester knows the availability page address for Marina Grand Hall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Confirm 'Venues' is not in the sidebar
-2. Paste the Marina Grand Hall availability page address into the browser address bar
-3. Press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Account: rachel.ng@meridianfina.com (Event Organiser)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>The page shows 'Venue availability is for ConnectSphere staff'.
-No grid, no bookings and no unavailable periods are shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="75" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Question / ambiguity for the PO or developer</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="179.5" customHeight="1">
-      <c r="A2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>SCREEN BUILT, AND THESE CASES HAVE BEEN EXECUTED. When they were drafted the calendar screen (S-21) did not exist, and they were written against the acceptance criteria as its specification; the screen landed in the same commit. The wording they name ('View availability', 'Show availability', 'Venue', 'From', 'To', 'Previous week', 'Next week', 'Free', 'Booked', 'Turnaround', 'Unavailable', 'Closed', 'Limited hours', 'Approved bookings', 'Unavailable periods', 'Room in use', 'Overlaps with') was checked against src/app/venues/[id]/availability/page.tsx and matches. Executed 2026-09-26 against a running server, after merging main: 21 of the 22 pass and TC14 is not executable (see below). One wording note for TC11 - 'Classroom' is the screen's label for the stored value 'classroom' (layoutLabel(), page.tsx); the API itself carries the raw value.</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="n"/>
-    </row>
-    <row r="3" ht="287.5" customHeight="1">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>DATES IN THIS FILE MATCH A DATABASE SEEDED ON 2026-09-26. RE-BASE THEM IF YOURS WAS SEEDED ON ANOTHER DAY. prisma/seed.ts builds every date as day(n) = the day it was run + n days, so every date under Preconditions, Test Data and Expected Result moves with each reseed; a tester on a different seed follows the steps, sees an empty grid, and reports a bug that isn't one. These cases were first written against a 2026-09-20 seed and were re-based +6 days on 2026-09-26, then verified case by case against a running server. To re-base again, add (your seed day - 2026-09-26) days to every date. Your seed day is the date `npx prisma db seed` was last run; to recover it from the data instead, the Jurong Expo Floor renovation period always begins on seed day + 21. Every fixture these cases use sits at a fixed offset in prisma/seed.ts, so the dates can also be rebuilt from the seed day directly: Rooftop Terrace free day = +15; Jurong Expo Floor renovation = +21 to +28; Harbourline Claims training = +23; Changi Meeting Room 2 cancelled booking = +33; Marina Auditorium rejected booking = +36; Bayu Energy panel = +44; Marina Boardroom 2 refurbishment = +60 to +74; Sundara Trade Showcase = +65; Straits Medical Symposium = +72; Pearl Delta pending request = +79; Meridian Wealth Forum = +85. Recorded as a Known Gap in DOCUMENTATION.md: it affects every story's test cases, not just this one, and a permanent fix needs a team decision.</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="n"/>
-    </row>
-    <row r="4" ht="125.5" customHeight="1">
-      <c r="A4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Team decision - how users reach the calendar: a 'View availability' link on every row of the Venues list, and a 'View availability' button on the venue edit page. The Venues list link is the one that matters for Event Coordinators, who hold the calendar permission but cannot open the edit page - their Venues list is read-only and its rows do not click - so a link on the edit page alone would have left the role this story most serves (identifying when venues may be requested, ahead of SPM-42) with no way in except typing the address. TC16 reaches the calendar through the Venues list link.</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n"/>
-    </row>
-    <row r="5" ht="85" customHeight="1">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>AC5 cannot be tested by hand. Nothing in the app can create a venue unavailable period - the Block venue screen (S-23) is not built and nothing writes to that table - and the five seeded periods are at five different venues, so none overlap. TC14 needs two overlapping periods added to the demo data before it can run. Today AC5 is covered by unit tests only.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="206.5" customHeight="1">
-      <c r="A6" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Team decision - slot boundaries: AM 06:00–12:00, PM 12:00–18:00, Night 18:00–23:00, no slot crossing midnight, the same grid for every venue. SPM-46 names the three slots but never defines their times, and nothing else in the project does, so the team set them. A venue's own opening hours mark a slot closed or partly open but do not move the boundaries: a fixed grid keeps venues comparable, and nothing defines where PM would start if AM started at each venue's opening time. AM starts at 06:00 rather than the first-proposed 08:00 because 08:00 was measured against the demo data and was too late: of 13 approved bookings, four fell partly outside the grid once setup time was added - up to 120 minutes each - because Jurong Expo Floor opens at 06:00 and Marina Grand Hall's 180-minute setup puts a 09:00 event in the room from 06:00. With AM at 06:00 all 13 fit the grid, and the Sundara Hospitality Trade Showcase went from 120 minutes outside to 0. TC07 and every expected slot in TC08-TC13 and TC19 rest on these times.</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="166" customHeight="1">
-      <c r="A7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Team decision - 'confirmed bookings' in AC3 and AC7 means a booking whose own status is Approved, not a booking whose event is Confirmed. VenueBooking has no 'confirmed' status; Approved is the state that commits the room. The calendar exists to prevent double-booking, and the event-status reading was checked against the demo data and fails that: the Straits Medical Research Symposium booking at Marina Grand Hall on 7 Dec 2026 is approved while its event is still in Planning, so under the event-status reading the room would show as free and invite a second booking - discovered only at approval time, since this story blocks SPM-42. The event's status is still shown with each booking for information. TC19 is the case that proves this; TC20 and TC21 confirm pending, rejected and cancelled bookings do not block a slot.</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Technical Support is internal staff, but cannot open the calendar (TC18) - the calendar reuses the venue catalogue's 'venue:view' permission, which Technical Support does not hold. AC6 says 'authorised internal users' without naming roles. Is excluding Technical Support intended?</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>What should a slot show when the room is open for only part of it? TC10 expects 'Free' with a 'Limited hours' note (One-North Rooftop Terrace opens at 16:00, so only 16:00–18:00 of PM is usable). The acceptance criteria do not cover opening hours at all.</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="85" customHeight="1">
-      <c r="A10" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>The S-21 mockup (design/mockups/VenueCalendar.dc.html) shows a continuous hour-by-hour grid, pending requests and 'tentative holds'. AC2 asks for AM/PM/Night slots, and the team chose to follow AC2. Pending requests are deliberately not shown (TC20), and 'tentative hold' does not exist anywhere in the data. Confirm the mockup is superseded for this screen.</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>A booking whose room time falls outside every slot (between 23:00 and 06:00) would not appear in the grid at all. Nothing in the demo data does this today, so no case covers it. How should the screen warn about it?</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Two checks the endpoint performs cannot be reached from a date picker and so have no test case: a date that does not exist (e.g. 31 Feb) and a date in the wrong format. The browser's date control cannot produce either.</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC18</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Logged in as Technical Support: kenji.sato@connectsphere.com / password123
-The tester knows the availability page address for Marina Grand Hall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Paste the Marina Grand Hall availability page address into the browser address bar
-2. Press Enter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Account: kenji.sato@connectsphere.com (Technical Support)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>The page shows 'Venue availability is for ConnectSphere staff'.
-No grid is shown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="85" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Demo data freshly loaded.
-Marina Grand Hall (MAR-GH) has an APPROVED booking, 'Straits Medical Research Symposium', 09:00–18:00 on 7 Dec 2026, whose EVENT is still in Planning - not Confirmed.
-Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the availability page for Marina Grand Hall
-2. Set 'From' and 'To' to the same date
-3. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Venue: Marina Grand Hall (MAR-GH)
-From: 7 Dec 2026
-To: 7 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>AM and PM show 'Booked' with 'Straits Medical Research Symposium' - NOT 'Free'.
-Night shows 'Turnaround' (teardown to 20:00).
-Under 'Approved bookings' the booking shows the event status 'Planning' and 'Room in use 06:00–20:00'.
-The room must not read as free: an approved booking already commits it, however far its event has got.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="71.5" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Demo data freshly loaded.
-Changi Conference Centre (CBP-CONF) has a PENDING booking request, 'Pearl Delta Safety Conference', on 14 Dec 2026, and no approved booking that day.
-Logged in as Event Coordinator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the availability page for Changi Conference Centre
-2. Set 'From' and 'To' to the same date
-3. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Venue: Changi Conference Centre (CBP-CONF)
-From: 14 Dec 2026
-To: 14 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>AM, PM and Night all show 'Free'.
-'Pearl Delta Safety Conference' does not appear under 'Approved bookings'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC21</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="85" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Demo data freshly loaded.
-Marina Auditorium (MAR-AUD) has a REJECTED booking for 'Nusantara Developer Summit' on 1 Nov 2026.
-Changi Meeting Room 2 (CBP-MTG2) has a CANCELLED booking for 'Pearl Delta Supplier Forum' on 29 Oct 2026.
-Logged in as Event Coordinator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the availability page for Marina Auditorium for 26 Oct 2026
-2. Choose Changi Meeting Room 2 from the 'Venue' picker
-3. Set 'From' and 'To' to 23 Oct 2026
-4. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Marina Auditorium (MAR-AUD): 1 Nov 2026
-Changi Meeting Room 2 (CBP-MTG2): 29 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Every slot at Marina Auditorium on 1 Nov 2026 shows 'Free', and 'Nusantara Developer Summit' is not listed.
-Every slot at Changi Meeting Room 2 on 29 Oct 2026 shows 'Free', and 'Pearl Delta Supplier Forum' is not listed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="58" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Demo data freshly loaded.
-Jurong Skills Lab (JUR-LAB) has no bookings.
-Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open Jurong Skills Lab from the Venues list
-2. Click 'Retire venue', then 'Retire venue' in the confirmation dialog
-3. Click 'View availability'
-4. Click 'Show availability'
-5. Return to the venue and click 'Restore venue' to undo the retirement</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Venue: Jurong Skills Lab (JUR-LAB)
-From: 7 Dec 2026
-To: 13 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>The availability page shows the warning 'This venue is retired'.
-Every slot shows 'Closed' - none shows 'Free'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -4129,7 +2572,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC01</t>
+          <t>SPM-46-TC02</t>
         </is>
       </c>
     </row>
@@ -4141,12 +2584,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>Logged in as Venue Staff: marcus.wong@connectsphere.com / password123
+Viewing Marina Grand Hall's availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4154,15 +2597,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Venues' in the sidebar
-2. Click the 'Marina Grand Hall' row
-3. Click 'View availability'
-4. Set 'From' and 'To'
-5. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Set 'From' to 11 Oct 2026
+2. Set 'To' to 7 Oct 2026
+3. Click 'Show availability'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4170,13 +2611,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Marina Grand Hall (MAR-GH)
-From: 7 Dec 2026
-To: 13 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>From: 11 Oct 2026
+To: 7 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4184,9 +2624,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The 'Marina Grand Hall availability' page opens.
-The grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026, each with AM, PM and Night columns.
-The 'Venue' picker shows Marina Grand Hall.</t>
+          <t>The message 'The end date must be on or after the start date.' is shown, and no grid is shown for the invalid range.</t>
         </is>
       </c>
     </row>
@@ -4209,7 +2647,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -4295,11 +2733,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC02</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
+          <t>SPM-46-TC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4307,11 +2745,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Logged in as Venue Staff: marcus.wong@connectsphere.com / password123
+Viewing Marina Grand Hall's availability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4319,13 +2758,14 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Venues' in the sidebar
-2. Click the 'Marina Grand Hall' row
-3. Click 'View availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+          <t>1. Set 'From' to 7 Oct 2026 and 'To' to 7 Dec 2026
+2. Click 'Show availability'
+3. Change 'To' to 8 Dec 2026
+4. Click 'Show availability'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4333,12 +2773,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Marina Grand Hall (MAR-GH)
-No From or To entered</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>From: 7 Oct 2026
+62 days — To: 7 Dec 2026
+63 days — To: 8 Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4346,8 +2787,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The grid shows seven day rows, starting today (Singapore time) and ending six days later.
-'From' and 'To' show those two dates.</t>
+          <t>With To = 7 Dec 2026 the grid shows 62 day rows, 7 Oct to 7 Dec 2026. With To = 8 Dec 2026 the message 'Choose a range of 62 days or fewer - this one is 63.' is shown and no grid is shown.</t>
         </is>
       </c>
     </row>
@@ -4370,7 +2810,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -4456,11 +2896,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC03</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44.5" customHeight="1">
+          <t>SPM-46-TC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4468,8 +2908,9 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data freshly loaded.
-Logged in as Venue Staff and viewing Marina Grand Hall's availability for 30 Nov 2026 to 6 Dec 2026.</t>
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123
+Viewing Marina Grand Hall's availability for 7–13 Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -4481,12 +2922,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Choose a different venue from the 'Venue' picker
-2. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Click 'Next week'
+2. Click 'Previous week' twice</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4494,9 +2935,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 30 Nov 2026
-To: 6 Dec 2026</t>
+          <t>Starting range: 7 Dec 2026 – 13 Dec 2026</t>
         </is>
       </c>
     </row>
@@ -4508,9 +2947,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The page title changes to 'Jurong Expo Floor availability'.
-The row for 30 Nov 2026 shows the 'Sundara Hospitality Trade Showcase' booking.
-The date range stays 30 Nov 2026 to 6 Dec 2026.</t>
+          <t>After 'Next week' the grid shows 14–20 Dec 2026, and the 20 Dec row shows the 'Meridian Wealth Management Forum' booking. After 'Previous week' twice the grid shows 30 Nov 2026 to 6 Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -4533,7 +2970,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -4619,11 +3056,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
+          <t>SPM-46-TC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4631,7 +3068,9 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Venue Staff and viewing Marina Grand Hall's availability.</t>
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+One-North Auditorium (ONE-AUD) has a 90-minute setup and an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 9 Nov 2026.
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
@@ -4643,13 +3082,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Set 'From' to the later date
-2. Set 'To' to the earlier date
+          <t>1. Open the availability page for One-North Auditorium
+2. Set 'From' and 'To' to the same date
 3. Click 'Show availability'</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="31" customHeight="1">
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4657,12 +3096,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>From: 11 Oct 2026
-To: 7 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>Venue: One-North Auditorium (ONE-AUD)
+From: 9 Nov 2026
+To: 9 Nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4670,8 +3110,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The message 'The end date must be on or after the start date.' is shown.
-No grid is shown for the invalid range.</t>
+          <t>AM shows 'Free'. PM shows 'Turnaround' — the event starts at 18:00, but setup puts the room in use from 16:30. Night shows 'Booked' with 'Bayu Energy Transition Panel'. Under 'Approved bookings' the booking shows 9 Nov 2026, 18:00–21:00 and 'Room in use 16:30–22:00'.</t>
         </is>
       </c>
     </row>
@@ -4694,7 +3133,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -4780,11 +3219,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC05</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
+          <t>SPM-46-TC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4792,11 +3231,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Venue Staff and viewing Marina Grand Hall's availability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Jurong Expo Floor (JUR-EXP) has a 240-minute setup and 180-minute teardown, and an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 30 Nov 2026.
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4804,10 +3245,9 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Set 'From' and 'To' for a 62-day range
-2. Click 'Show availability'
-3. Change 'To' one day later
-4. Click 'Show availability'</t>
+          <t>1. Open the availability page for Jurong Expo Floor
+2. Set 'From' and 'To' to the same date
+3. Click 'Show availability'</t>
         </is>
       </c>
     </row>
@@ -4819,13 +3259,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>From: 7 Oct 2026
-62 days - To: 7 Dec 2026
-63 days - To: 8 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>Venue: Jurong Expo Floor (JUR-EXP)
+From: 30 Nov 2026
+To: 30 Nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4833,8 +3273,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>With To = 7 Dec 2026, the grid shows 62 day rows, 7 Oct to 7 Dec 2026.
-With To = 8 Dec 2026, the message 'Choose a range of 62 days or fewer - this one is 63.' is shown and no grid is shown.</t>
+          <t>AM shows 'Booked' and PM shows 'Booked', each with 'Sundara Hospitality Trade Showcase'. Night shows 'Turnaround' — the event ends at 18:00, but teardown keeps the room in use until 21:00. Under 'Approved bookings' the booking shows 'Room in use 06:00–21:00'.</t>
         </is>
       </c>
     </row>
@@ -4857,7 +3296,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -4943,11 +3382,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="31" customHeight="1">
+          <t>SPM-46-TC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4955,11 +3394,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Venue Staff and viewing Marina Grand Hall's availability for 7-13 Dec 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+One-North Rooftop Terrace (ONE-ROOF) is open 16:00–23:00 only, and has no bookings on this date.
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4967,12 +3408,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Next week'
-2. Click 'Previous week' twice</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
+          <t>1. Open the availability page for One-North Rooftop Terrace
+2. Set 'From' and 'To' to 11 Oct 2026
+3. Click 'Show availability'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4980,11 +3422,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Starting range: 7 Dec 2026 - 13 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Venue: One-North Rooftop Terrace (ONE-ROOF)
+From: 11 Oct 2026
+To: 11 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4992,8 +3436,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>After 'Next week' the grid shows 14-20 Dec 2026, and the 20 Dec row shows the 'Meridian Wealth Management Forum' booking.
-After 'Previous week' twice the grid shows 30 Nov 2026 to 6 Dec 2026.</t>
+          <t>AM shows 'Closed' — the terrace is shut for the whole of 06:00–12:00. PM shows 'Free' with the note 'Limited hours' — it is open only from 16:00. Night shows 'Free' with no note.</t>
         </is>
       </c>
     </row>
@@ -5016,7 +3459,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">
@@ -5102,11 +3545,11 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>SPM-46-TC07</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.5" customHeight="1">
+          <t>SPM-46-TC08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -5114,11 +3557,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Venue Staff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Jurong Expo Floor (JUR-EXP) is recorded as unavailable for renovation from 17 Oct 2026 to 24 Oct 2026.
+Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -5126,12 +3571,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for any venue
-2. Read the grid's column headings</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
+          <t>1. Open the availability page for Jurong Expo Floor
+2. Set 'From' to 17 Oct 2026 and 'To' to 23 Oct 2026
+3. Click 'Show availability'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -5139,7 +3585,9 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Marina Grand Hall (MAR-GH)</t>
+          <t>Venue: Jurong Expo Floor (JUR-EXP)
+From: 17 Oct 2026
+To: 23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -5151,11 +3599,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The grid has exactly three columns, in this order, each showing its times:
-AM 06:00–12:00
-PM 12:00–18:00
-Night 18:00–23:00
-The same three columns appear for every venue.</t>
+          <t>Every slot on every day from 17 to 23 Oct 2026 shows 'Unavailable' — 21 cells, none of them 'Free'. Under 'Unavailable periods' one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026, with no 'Overlaps with' note and no overlap warning above the grid.</t>
         </is>
       </c>
     </row>
@@ -5178,7 +3622,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46287</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="10">

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Setup time puts the room in use before the event, in the earlier slot</t>
+          <t>A Night event's setup takes the whole PM slot, and its turnaround the next day's AM</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Teardown keeps the room in use after the event, into the later slot</t>
+          <t>An event's setup takes the whole slot before it, on the previous day where needed</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>A venue's opening hours mark slots Closed or Limited hours</t>
+          <t>A venue's opening hours mark slots Closed, or name the hours it is open</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1941,7 +1941,7 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the availability page for Marina Grand Hall
-2. Set 'From' and 'To' to the same date
+2. Set 'From' to 6 Dec 2026 and 'To' to 7 Dec 2026
 3. Click 'Show availability'
 4. Read the booking under 'Approved bookings'</t>
         </is>
@@ -1956,12 +1956,12 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Marina Grand Hall (MAR-GH)
-From: 7 Dec 2026
+From: 6 Dec 2026
 To: 7 Dec 2026</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="98.5" customHeight="1">
+    <row r="6" ht="125.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free'. Night shows 'Turnaround' (teardown to 20:00). Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use 06:00–20:00'. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
+          <t>On 7 Dec 2026 AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free' — and Night shows 'Turnaround'. On 6 Dec 2026 Night shows 'Turnaround' too, for the setup slot before the event. Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use' from 6 Dec 2026, 19:00 to 8 Dec 2026, 00:00. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The 'Marina Grand Hall availability' page opens on a week from today (Singapore time): seven day rows, with 'From' and 'To' already filled in with those two dates. The grid has exactly three columns, in this order, each showing its times: AM 06:00–12:00, PM 12:00–18:00, Night 18:00–23:00. After 'Show availability' the grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026 (the 7 Dec row is not empty — it carries the Straits Medical Research Symposium booking). Choosing Jurong Expo Floor changes the title to 'Jurong Expo Floor availability', keeps the range at 7–13 Dec 2026, and shows the same three columns.</t>
+          <t>The 'Marina Grand Hall availability' page opens on a week from today (Singapore time): seven day rows, with 'From' and 'To' already filled in with those two dates. The grid has exactly three columns, in this order, each showing its times: AM 07:00–12:00, PM 13:00–18:00, Night 19:00–24:00. After 'Show availability' the grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026 (the 7 Dec row is not empty — it carries the Straits Medical Research Symposium booking). Choosing Jurong Expo Floor changes the title to 'Jurong Expo Floor availability', keeps the range at 7–13 Dec 2026, and shows the same three columns.</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
-One-North Auditorium (ONE-AUD) has a 90-minute setup and an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 9 Nov 2026.
+One-North Auditorium (ONE-AUD) records setup and teardown time, and has an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 9 Nov 2026.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -3083,7 +3083,7 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the availability page for One-North Auditorium
-2. Set 'From' and 'To' to the same date
+2. Set 'From' to 9 Nov 2026 and 'To' to 10 Nov 2026
 3. Click 'Show availability'</t>
         </is>
       </c>
@@ -3098,11 +3098,11 @@
         <is>
           <t>Venue: One-North Auditorium (ONE-AUD)
 From: 9 Nov 2026
-To: 9 Nov 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+To: 10 Nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM shows 'Free'. PM shows 'Turnaround' — the event starts at 18:00, but setup puts the room in use from 16:30. Night shows 'Booked' with 'Bayu Energy Transition Panel'. Under 'Approved bookings' the booking shows 9 Nov 2026, 18:00–21:00 and 'Room in use 16:30–22:00'.</t>
+          <t>On 9 Nov 2026: AM shows 'Free'. PM shows 'Turnaround' — the whole slot before the event is taken for setup. Night shows 'Booked' with 'Bayu Energy Transition Panel'. On 10 Nov 2026: AM shows 'Turnaround' — the turnaround runs into the NEXT DAY, because Night is the last slot of its own day; PM and Night show 'Free'. Under 'Approved bookings' the booking shows 18:00–21:00 with 'Room in use' running from 9 Nov 2026, 13:00 to 10 Nov 2026, 12:00 — whole slots, not the recorded minutes.</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
-Jurong Expo Floor (JUR-EXP) has a 240-minute setup and 180-minute teardown, and an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 30 Nov 2026.
+Jurong Expo Floor (JUR-EXP) records setup and teardown time, and has an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 30 Nov 2026.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -3246,7 +3246,7 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' and 'To' to the same date
+2. Set 'From' to 29 Nov 2026 and 'To' to 30 Nov 2026
 3. Click 'Show availability'</t>
         </is>
       </c>
@@ -3260,12 +3260,12 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 30 Nov 2026
+From: 29 Nov 2026
 To: 30 Nov 2026</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="71.5" customHeight="1">
+    <row r="6" ht="112" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM shows 'Booked' and PM shows 'Booked', each with 'Sundara Hospitality Trade Showcase'. Night shows 'Turnaround' — the event ends at 18:00, but teardown keeps the room in use until 21:00. Under 'Approved bookings' the booking shows 'Room in use 06:00–21:00'.</t>
+          <t>On 29 Nov 2026: AM and PM show 'Free', and Night shows 'Turnaround' — the event is in the morning, so the slot before it is the PREVIOUS DAY'S Night. On 30 Nov 2026: AM and PM show 'Booked' with 'Sundara Hospitality Trade Showcase' (the event runs 10:00–18:00, and a slot touched at all is taken in full), and Night shows 'Turnaround'. Under 'Approved bookings', 'Room in use' runs from 29 Nov 2026, 19:00 to 1 Dec 2026, 00:00.</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44.5" customHeight="1">
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AM shows 'Closed' — the terrace is shut for the whole of 06:00–12:00. PM shows 'Free' with the note 'Limited hours' — it is open only from 16:00. Night shows 'Free' with no note.</t>
+          <t>AM shows 'Closed' — the terrace is shut for the whole of 07:00–12:00. PM shows 'Free' with the note 'Open from 16:00' — only 16:00–18:00 of that slot is bookable. Night shows 'Free' with the note 'Open until 23:00' — the slot runs to midnight but the terrace closes at 23:00.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -1432,7 +1432,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="139" customHeight="1">
+    <row r="3" ht="166" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1440,12 +1440,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>BLOCKED — NOT RUNNABLE ON THE DEMO DATA. Nothing in the app can create a venue unavailable period: the Block venue screen (S-23) is not built and no route writes to that table, and the five seeded periods sit at five different venues, so none overlap. Two overlapping periods must be added to prisma/seed.ts before this can run. The rule itself is covered by the unit tests in src/lib/__tests__/venueAvailability.test.ts. Recorded under Known Gaps in DOCUMENTATION.md.
+          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+Jurong Expo Floor (JUR-EXP) has TWO unavailable periods that overlap each other: 'Loading bay hoist inspection.' (maintenance) 5–9 Nov 2026, and 'Fire suppression system recertification.' (safety) 7–11 Nov 2026. They are the only overlapping pair in the demo data — nothing in the app can create one until the Block venue screen (S-23) is built, so they are seeded.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.5" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1454,12 +1455,13 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' and 'To' to cover both periods
-3. Click 'Show availability'</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="71.5" customHeight="1">
+2. Set 'From' to 5 Nov 2026 and 'To' to 11 Nov 2026
+3. Click 'Show availability'
+4. Read the 'Unavailable periods' list</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1468,14 +1470,12 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-Period A: 18 Oct 2026 08:00–14:00, maintenance
-Period B: 18 Oct 2026 12:00–18:00, safety
-From: 18 Oct 2026
-To: 18 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+From: 5 Nov 2026
+To: 11 Nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid, and under 'Unavailable periods' each of the two periods is marked 'Overlaps with' the other.</t>
+          <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid. Under 'Unavailable periods' both are listed — 'Maintenance', 'Loading bay hoist inspection.' and 'Safety', 'Fire suppression system recertification.' — and EACH carries an 'Overlaps with' note naming the other. Every slot from 5 to 11 Nov 2026 shows 'Unavailable', since between them the two periods cover the whole range.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Pending, rejected and cancelled bookings never block a slot</t>
+          <t>Only an approved booking takes a slot; a pending request is shown but does not</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="152.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2132,7 +2132,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.</t>
+          <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.
+On 14 Dec 2026 the Changi Conference Centre slots additionally carry the note 'Requested: Pearl Delta Safety Conference', and a card 'Requested, not yet approved' lists it below the grid. The slots stay 'Free' — a request is not a commitment — but the hold is visible so a second coordinator does not request the same room unaware. The rejected and cancelled bookings carry no such note: they are not live requests.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -1636,7 +1636,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The 'Marina Grand Hall availability' page opens and shows the grid for both accounts. Clicking elsewhere on the row does nothing — the Venues list stays read-only for a coordinator.</t>
+          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="85" customHeight="1">
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1778,9 +1778,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Sign in as the Event Organiser and confirm 'Venues' is not in the sidebar
-2. Paste the Marina Grand Hall availability page address into the address bar and press Enter
-3. Sign out, sign in as Technical Support, and open the same address</t>
+          <t>1. Sign in as the Event Organiser
+2. Confirm there is no 'Venues' item in the sidebar
+3. Paste the Marina Grand Hall availability page address into the address bar and press Enter
+4. Sign out and sign in as Technical Support
+5. Confirm there is no 'Venues' item in their sidebar either
+6. Open the same address again</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1800,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="71.5" customHeight="1">
+    <row r="6" ht="166" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1805,7 +1808,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>For both accounts the page shows 'Venue availability is for ConnectSphere staff'. No grid, no bookings and no unavailable periods are shown. Technical Support is internal staff but still has no access, because the calendar reuses the venue catalogue's permission.</t>
+          <t>Neither account has 'Venues' in the sidebar, so neither can reach the calendar by navigating — an Event Organiser sees Dashboard, My Events and Notifications; Technical Support sees Dashboard, Equipment, Equipment Requests and Notifications.
+Typing the address directly is refused as well: the page shows 'Venue availability is for ConnectSphere staff', with no grid, no bookings and no unavailable periods. Hiding the link is not the control — the server refuses it too. Technical Support is internal staff and still has no access, because the calendar reuses the venue catalogue's permission, which they do not hold.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -21,7 +21,6 @@
     <sheet name="TC12" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="TC13" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="TC14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="TC15" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -461,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -757,7 +756,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>A recorded unavailable period covers every slot it spans</t>
+          <t>An unavailable period covers every slot from its first day to its last, and no further</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -767,7 +766,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Boundary</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -789,17 +788,17 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>A multi-day unavailable period stops on its last day</t>
+          <t>Two overlapping unavailable periods are identified as overlapping</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>AC4</t>
+          <t>AC5</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -821,12 +820,12 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Two overlapping unavailable periods are identified as overlapping</t>
+          <t>An Event Coordinator and an Operations Manager can open the calendar</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC6</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -853,7 +852,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>An Event Coordinator and an Operations Manager can open the calendar</t>
+          <t>A role without venue permissions cannot open the calendar</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -863,7 +862,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -885,17 +884,17 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>A role without venue permissions cannot open the calendar</t>
+          <t>An approved booking blocks its slots, and is listed, even while its event is still in planning</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>AC6</t>
+          <t>AC3, AC7</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -917,17 +916,17 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>An approved booking blocks its slots, and is listed, even while its event is still in planning</t>
+          <t>Only an approved booking takes a slot; a pending request is shown but does not</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>AC3, AC7</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -949,7 +948,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Only an approved booking takes a slot; a pending request is shown but does not</t>
+          <t>A retired venue's slots are never offered as free</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -968,72 +967,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>TC15</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC15</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>A retired venue's slots are never offered as free</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Acceptance Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Covered by</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>AC1</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Users can select a venue and date/time period.</t>
         </is>
       </c>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="9" t="n"/>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Covered by</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>AC1</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Users can select a venue and date/time period.</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>SPM-46-TC01
 SPM-46-TC02
@@ -1041,22 +1008,22 @@
 SPM-46-TC04</t>
         </is>
       </c>
-      <c r="F22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="F21" s="9" t="n"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Availability is shown per fixed slot (AM, PM, Night) for each day, including slots occupied by setup or turnaround time.</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>SPM-46-TC01
 SPM-46-TC05
@@ -1064,119 +1031,118 @@
 SPM-46-TC07</t>
         </is>
       </c>
+      <c r="F22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>AC3</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Existing confirmed bookings are displayed.</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>SPM-46-TC12</t>
+        </is>
+      </c>
       <c r="F23" s="9" t="n"/>
     </row>
     <row r="24" ht="17.5" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>AC3</t>
+          <t>AC4</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Existing confirmed bookings are displayed.</t>
+          <t>Recorded unavailable periods are displayed.</t>
         </is>
       </c>
       <c r="C24" s="8" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>SPM-46-TC13</t>
+          <t>SPM-46-TC08</t>
         </is>
       </c>
       <c r="F24" s="9" t="n"/>
     </row>
-    <row r="25" ht="31" customHeight="1">
+    <row r="25" ht="17.5" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>AC4</t>
+          <t>AC5</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Recorded unavailable periods are displayed.</t>
+          <t>Overlapping unavailable periods are identifiable.</t>
         </is>
       </c>
       <c r="C25" s="8" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>SPM-46-TC08
-SPM-46-TC09</t>
+          <t>SPM-46-TC09</t>
         </is>
       </c>
       <c r="F25" s="9" t="n"/>
     </row>
-    <row r="26" ht="17.5" customHeight="1">
+    <row r="26" ht="31" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>AC5</t>
+          <t>AC6</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Overlapping unavailable periods are identifiable.</t>
+          <t>Only authorised internal users can access the availability calendar.</t>
         </is>
       </c>
       <c r="C26" s="8" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>SPM-46-TC10</t>
+          <t>SPM-46-TC10
+SPM-46-TC11</t>
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
     </row>
-    <row r="27" ht="31" customHeight="1">
+    <row r="27" ht="44.5" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>AC6</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Only authorised internal users can access the availability calendar.</t>
+          <t>Availability reflects confirmed bookings.</t>
         </is>
       </c>
       <c r="C27" s="8" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>SPM-46-TC11
-SPM-46-TC12</t>
+          <t>SPM-46-TC12
+SPM-46-TC13
+SPM-46-TC14</t>
         </is>
       </c>
       <c r="F27" s="9" t="n"/>
     </row>
-    <row r="28" ht="44.5" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Availability reflects confirmed bookings.</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>SPM-46-TC13
-SPM-46-TC14
-SPM-46-TC15</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="30" ht="125.5" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="29" ht="125.5" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>src/app/api/venues/[id]/availability/route.ts
 src/lib/venueAvailability.ts
@@ -1189,17 +1155,18 @@
 design/mockups/VenueCalendar.dc.html</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="9" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="B26:D26"/>
@@ -1209,11 +1176,10 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="E28:F28"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1230,7 +1196,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1269,7 +1234,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="166" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1277,13 +1242,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
-Marina Boardroom 2 (MAR-BR2) is recorded as unavailable for renovation from 25 Nov 2026 to 9 Dec 2026, ending 23:59 on 9 Dec.
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
+Jurong Expo Floor (JUR-EXP) has TWO unavailable periods that overlap each other: 'Loading bay hoist inspection.' (maintenance) 5–9 Nov 2026, and 'Fire suppression system recertification.' (safety) 7–11 Nov 2026. They are the only overlapping pair in the demo data — nothing in the app can create one until the Block venue screen (S-23) is built, so they are seeded. If they are missing from the shared database, run: npx tsx prisma/topup-spm40-46.ts (adds them without a reseed).
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.5" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1291,9 +1256,10 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Marina Boardroom 2
-2. Set 'From' to 7 Dec 2026 and 'To' to 13 Dec 2026
-3. Click 'Show availability'</t>
+          <t>1. Open the availability page for Jurong Expo Floor
+2. Set 'From' to 5 Nov 2026 and 'To' to 11 Nov 2026
+3. Click 'Show availability'
+4. Read the 'Unavailable periods' list</t>
         </is>
       </c>
     </row>
@@ -1305,13 +1271,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Marina Boardroom 2 (MAR-BR2)
-From: 7 Dec 2026
-To: 13 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Venue: Jurong Expo Floor (JUR-EXP)
+From: 5 Nov 2026
+To: 11 Nov 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1319,7 +1285,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Every slot on 7, 8 and 9 Dec 2026 shows 'Unavailable'. Every slot from 10 to 13 Dec 2026 shows 'Free' — the period stops on its last day and does not spill into 10 Dec. 'Unavailable periods' lists it as 'Refurbishment of the boardroom fit-out.', 25 Nov to 9 Dec 2026.</t>
+          <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid. Under 'Unavailable periods' both are listed — 'Maintenance', 'Loading bay hoist inspection.' and 'Safety', 'Fire suppression system recertification.' — and EACH carries an 'Overlaps with' note naming the other. Every slot from 5 to 11 Nov 2026 shows 'Unavailable', since between them the two periods cover the whole range.</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1398,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="166" customHeight="1">
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1440,13 +1406,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
-Jurong Expo Floor (JUR-EXP) has TWO unavailable periods that overlap each other: 'Loading bay hoist inspection.' (maintenance) 5–9 Nov 2026, and 'Fire suppression system recertification.' (safety) 7–11 Nov 2026. They are the only overlapping pair in the demo data — nothing in the app can create one until the Block venue screen (S-23) is built, so they are seeded.
-Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
+          <t>Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1454,10 +1418,10 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' to 5 Nov 2026 and 'To' to 11 Nov 2026
-3. Click 'Show availability'
-4. Read the 'Unavailable periods' list</t>
+          <t>1. Click 'Venues' in the sidebar
+2. On the 'Marina Grand Hall' row, click 'View availability'
+3. Go back to 'Venues' and click elsewhere on the 'Marina Grand Hall' row
+4. Sign out, sign in as the Operations Manager, and repeat the first two steps</t>
         </is>
       </c>
     </row>
@@ -1469,13 +1433,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 5 Nov 2026
-To: 11 Nov 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="98.5" customHeight="1">
+          <t>Accounts: daniel.tan@connectsphere.com (Event Coordinator), grace.lim@connectsphere.com (Operations Manager)
+Venue: Marina Grand Hall (MAR-GH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1483,7 +1446,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid. Under 'Unavailable periods' both are listed — 'Maintenance', 'Loading bay hoist inspection.' and 'Safety', 'Fire suppression system recertification.' — and EACH carries an 'Overlaps with' note naming the other. Every slot from 5 to 11 Nov 2026 shows 'Unavailable', since between them the two periods cover the whole range.</t>
+          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1559,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1604,11 +1567,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
+          <t>The tester knows the availability page address for Marina Grand Hall.
+Accounts available: rachel.ng@meridianfina.com (Event Organiser) and kenji.sato@connectsphere.com (Technical Support), both / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1616,14 +1580,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Click 'Venues' in the sidebar
-2. On the 'Marina Grand Hall' row, click 'View availability'
-3. Go back to 'Venues' and click elsewhere on the 'Marina Grand Hall' row
-4. Sign out, sign in as the Operations Manager, and repeat the first two steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
+          <t>1. Sign in as the Event Organiser
+2. Confirm there is no 'Venues' item in the sidebar
+3. Paste the Marina Grand Hall availability page address into the address bar and press Enter
+4. Sign out and sign in as Technical Support
+5. Confirm there is no 'Venues' item in their sidebar either
+6. Open the same address again</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1631,12 +1597,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Accounts: daniel.tan@connectsphere.com (Event Coordinator), grace.lim@connectsphere.com (Operations Manager)
-Venue: Marina Grand Hall (MAR-GH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="71.5" customHeight="1">
+          <t>Account: rachel.ng@meridianfina.com (Event Organiser)
+Account: kenji.sato@connectsphere.com (Technical Support)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="166" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1644,7 +1610,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
+          <t>Neither account has 'Venues' in the sidebar, so neither can reach the calendar by navigating — an Event Organiser sees Dashboard, My Events and Notifications; Technical Support sees Dashboard, Equipment, Equipment Requests and Notifications.
+Typing the address directly is refused as well: the page shows 'Venue availability is for ConnectSphere staff', with no grid, no bookings and no unavailable periods. Hiding the link is not the control — the server refuses it too. Technical Support is internal staff and still has no access, because the calendar reuses the venue catalogue's permission, which they do not hold.</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1724,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1765,12 +1732,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The tester knows the availability page address for Marina Grand Hall.
-Accounts available: rachel.ng@meridianfina.com (Event Organiser) and kenji.sato@connectsphere.com (Technical Support), both / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98.5" customHeight="1">
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
+Marina Grand Hall (MAR-GH) has an APPROVED booking, 'Straits Medical Research Symposium', 09:00–18:00 on 7 Dec 2026, whose EVENT is still in Planning — not Confirmed. The venue has a 180-minute setup and 120-minute teardown.
+Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1778,16 +1746,14 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Sign in as the Event Organiser
-2. Confirm there is no 'Venues' item in the sidebar
-3. Paste the Marina Grand Hall availability page address into the address bar and press Enter
-4. Sign out and sign in as Technical Support
-5. Confirm there is no 'Venues' item in their sidebar either
-6. Open the same address again</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+          <t>1. Open the availability page for Marina Grand Hall
+2. Set 'From' to 6 Dec 2026 and 'To' to 7 Dec 2026
+3. Click 'Show availability'
+4. Read the booking under 'Approved bookings'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1795,12 +1761,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Account: rachel.ng@meridianfina.com (Event Organiser)
-Account: kenji.sato@connectsphere.com (Technical Support)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="166" customHeight="1">
+          <t>Venue: Marina Grand Hall (MAR-GH)
+From: 6 Dec 2026
+To: 7 Dec 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1808,8 +1775,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Neither account has 'Venues' in the sidebar, so neither can reach the calendar by navigating — an Event Organiser sees Dashboard, My Events and Notifications; Technical Support sees Dashboard, Equipment, Equipment Requests and Notifications.
-Typing the address directly is refused as well: the page shows 'Venue availability is for ConnectSphere staff', with no grid, no bookings and no unavailable periods. Hiding the link is not the control — the server refuses it too. Technical Support is internal staff and still has no access, because the calendar reuses the venue catalogue's permission, which they do not hold.</t>
+          <t>On 7 Dec 2026 AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free' — and Night shows 'Turnaround'. On 6 Dec 2026 Night shows 'Turnaround' too, for the setup slot before the event. Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use' from 6 Dec 2026, 19:00 to 8 Dec 2026, 00:00. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1888,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="125.5" customHeight="1">
+    <row r="3" ht="139" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1930,13 +1896,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
-Marina Grand Hall (MAR-GH) has an APPROVED booking, 'Straits Medical Research Symposium', 09:00–18:00 on 7 Dec 2026, whose EVENT is still in Planning — not Confirmed. The venue has a 180-minute setup and 120-minute teardown.
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
+Changi Conference Centre (CBP-CONF) has a PENDING booking request, 'Pearl Delta Safety Conference', on 14 Dec 2026 and no approved booking that day. Marina Auditorium (MAR-AUD) has a REJECTED booking for 'Nusantara Developer Summit' on 1 Nov 2026. Changi Meeting Room 2 (CBP-MTG2) has a CANCELLED booking for 'Pearl Delta Supplier Forum' on 29 Oct 2026.
 Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1944,10 +1910,9 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Open the availability page for Marina Grand Hall
-2. Set 'From' to 6 Dec 2026 and 'To' to 7 Dec 2026
-3. Click 'Show availability'
-4. Read the booking under 'Approved bookings'</t>
+          <t>1. Open the availability page for Changi Conference Centre for 14 Dec 2026
+2. Choose Marina Auditorium from the 'Venue' picker and show 1 Nov 2026
+3. Choose Changi Meeting Room 2 from the 'Venue' picker and show 29 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -1959,13 +1924,13 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue: Marina Grand Hall (MAR-GH)
-From: 6 Dec 2026
-To: 7 Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="125.5" customHeight="1">
+          <t>Changi Conference Centre (CBP-CONF): 14 Dec 2026
+Marina Auditorium (MAR-AUD): 1 Nov 2026
+Changi Meeting Room 2 (CBP-MTG2): 29 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="152.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1973,7 +1938,8 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>On 7 Dec 2026 AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free' — and Night shows 'Turnaround'. On 6 Dec 2026 Night shows 'Turnaround' too, for the setup slot before the event. Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use' from 6 Dec 2026, 19:00 to 8 Dec 2026, 00:00. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
+          <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.
+On 14 Dec 2026 the Changi Conference Centre slots additionally carry the note 'Requested: Pearl Delta Safety Conference', and a card 'Requested, not yet approved' lists it below the grid. The slots stay 'Free' — a request is not a commitment — but the hold is visible so a second coordinator does not request the same room unaware. The rejected and cancelled bookings carry no such note: they are not live requests.</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2052,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="152.5" customHeight="1">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2094,171 +2060,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
-Changi Conference Centre (CBP-CONF) has a PENDING booking request, 'Pearl Delta Safety Conference', on 14 Dec 2026 and no approved booking that day. Marina Auditorium (MAR-AUD) has a REJECTED booking for 'Nusantara Developer Summit' on 1 Nov 2026. Changi Meeting Room 2 (CBP-MTG2) has a CANCELLED booking for 'Pearl Delta Supplier Forum' on 29 Oct 2026.
-Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>1. Open the availability page for Changi Conference Centre for 14 Dec 2026
-2. Choose Marina Auditorium from the 'Venue' picker and show 1 Nov 2026
-3. Choose Changi Meeting Room 2 from the 'Venue' picker and show 29 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44.5" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Changi Conference Centre (CBP-CONF): 14 Dec 2026
-Marina Auditorium (MAR-AUD): 1 Nov 2026
-Changi Meeting Room 2 (CBP-MTG2): 29 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="152.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.
-On 14 Dec 2026 the Changi Conference Centre slots additionally carry the note 'Requested: Pearl Delta Safety Conference', and a card 'Requested, not yet approved' lists it below the grid. The slots stay 'Free' — a request is not a commitment — but the hold is visible so a second coordinator does not request the same room unaware. The rejected and cancelled bookings carry no such note: they are not live requests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17.5" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Creation Date</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>46291</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Date of Execution</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="24.77734375" customWidth="1" min="1" max="1"/>
-    <col width="56.77734375" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="17.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SPM-46-TC15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="85" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Jurong Skills Lab (JUR-LAB) is active and has no bookings.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
@@ -2415,7 +2217,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="71.5" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2423,7 +2225,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
@@ -2905,7 +2707,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="85" customHeight="1">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2913,7 +2715,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123
 Viewing Marina Grand Hall's availability for 7–13 Dec 2026.</t>
         </is>
@@ -3065,7 +2867,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3073,7 +2875,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 One-North Auditorium (ONE-AUD) records setup and teardown time, and has an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 9 Nov 2026.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
@@ -3228,7 +3030,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="112" customHeight="1">
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3236,7 +3038,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Jurong Expo Floor (JUR-EXP) records setup and teardown time, and has an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 30 Nov 2026.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
@@ -3391,7 +3193,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="98.5" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3399,7 +3201,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 One-North Rooftop Terrace (ONE-ROOF) is open 16:00–23:00 only, and has no bookings on this date.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
@@ -3554,7 +3356,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="98.5" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3562,13 +3364,13 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Demo data seeded 2026-09-26 — the dates below move with the seed, because prisma/seed.ts builds them as today + n days (see DOCUMENTATION.md, Known Gaps).
-Jurong Expo Floor (JUR-EXP) is recorded as unavailable for renovation from 17 Oct 2026 to 24 Oct 2026.
+          <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
+Jurong Expo Floor (JUR-EXP) is recorded as unavailable for renovation from 17 Oct 2026, 00:00 to 24 Oct 2026, 23:59, and has nothing else from 16 to 25 Oct 2026. It is open 06:00–23:00.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44.5" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3577,8 +3379,9 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Open the availability page for Jurong Expo Floor
-2. Set 'From' to 17 Oct 2026 and 'To' to 23 Oct 2026
-3. Click 'Show availability'</t>
+2. Set 'From' to 16 Oct 2026 and 'To' to 25 Oct 2026
+3. Click 'Show availability'
+4. Read the 'Unavailable periods' list</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3394,12 @@
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
-From: 17 Oct 2026
-To: 23 Oct 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="85" customHeight="1">
+From: 16 Oct 2026
+To: 25 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3604,7 +3407,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Every slot on every day from 17 to 23 Oct 2026 shows 'Unavailable' — 21 cells, none of them 'Free'. Under 'Unavailable periods' one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026, with no 'Overlaps with' note and no overlap warning above the grid.</t>
+          <t>16 Oct 2026: AM, PM and Night all show 'Free' (Night with the note 'Open until 23:00') — the period does not start early. 17 to 24 Oct 2026: every slot shows 'Unavailable' — 24 cells, none of them 'Free'. 25 Oct 2026: AM, PM and Night all show 'Free' again — the period stops on its last day and does not spill into the next. Under 'Unavailable periods' exactly one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026, with no 'Overlaps with' note and no overlap warning above the grid.</t>
         </is>
       </c>
     </row>

--- a/docs/test-cases/SPM-46_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-46_Test_Cases.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -53,6 +53,9 @@
       <color rgb="FF1155CC"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -138,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -189,6 +192,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,12 +487,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="20">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>SPM-46: As an authorised internal user, I want to view venue availability over relevant dates and times so that I can identify when venues may be requested</t>
         </is>
@@ -498,32 +504,32 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -550,27 +556,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC01</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Open a venue's availability and read the grid</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -593,27 +599,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC02</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>An end date before the start date is rejected</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -632,27 +638,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC03</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>A range of 62 days is accepted and 63 days is rejected</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -671,27 +677,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC04</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Previous week and Next week move the range by seven days</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -710,27 +716,27 @@
           <t>RETIRED – TC05</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC05</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>A Night event's setup takes the whole PM slot, and its turnaround the next day's AM</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -757,27 +763,27 @@
           <t>RETIRED – TC06</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC06</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>An event's setup takes the whole slot before it, on the previous day where needed</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -804,27 +810,27 @@
           <t>RETIRED – TC07</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC07</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>A venue's opening hours mark slots Closed, or name the hours it is open</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -851,27 +857,27 @@
           <t>RETIRED – TC08</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC08</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>An unavailable period covers every slot from its first day to its last, and no further</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -898,27 +904,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC09</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Two overlapping unavailable periods are identified as overlapping</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -941,38 +947,42 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC10</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>An Event Coordinator and an Operations Manager can open the calendar</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H13" s="24" t="n"/>
-      <c r="I13" s="24" t="n"/>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -980,27 +990,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC11</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>A role without venue permissions cannot open the calendar</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1019,27 +1029,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC12</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>An approved booking blocks its slots, and is listed, even while its event is still in planning</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>AC3, AC7</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1062,27 +1072,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC13</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Only an approved booking takes a slot; a pending request is shown but does not</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1105,27 +1115,27 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC14</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>A retired venue's slots are never offered as free</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1143,20 +1153,21 @@
       </c>
     </row>
     <row r="18"/>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C20" s="21" t="n"/>
       <c r="D20" s="22" t="n"/>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1164,19 +1175,19 @@
       <c r="F20" s="22" t="n"/>
     </row>
     <row r="21" ht="57.75" customHeight="1" s="20">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Users can select a venue and date/time period.</t>
         </is>
       </c>
       <c r="C21" s="21" t="n"/>
       <c r="D21" s="22" t="n"/>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC01
 SPM-46-TC02
@@ -1187,19 +1198,19 @@
       <c r="F21" s="22" t="n"/>
     </row>
     <row r="22" ht="57.75" customHeight="1" s="20">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Availability is shown per fixed slot (AM, PM, Night) for each day, including slots occupied by setup or turnaround time.</t>
         </is>
       </c>
       <c r="C22" s="21" t="n"/>
       <c r="D22" s="22" t="n"/>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC01
 SPM-46-TC05
@@ -1210,19 +1221,19 @@
       <c r="F22" s="22" t="n"/>
     </row>
     <row r="23" ht="17.25" customHeight="1" s="20">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Existing confirmed bookings are displayed.</t>
         </is>
       </c>
       <c r="C23" s="21" t="n"/>
       <c r="D23" s="22" t="n"/>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC12</t>
         </is>
@@ -1230,19 +1241,19 @@
       <c r="F23" s="22" t="n"/>
     </row>
     <row r="24" ht="17.25" customHeight="1" s="20">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Recorded unavailable periods are displayed.</t>
         </is>
       </c>
       <c r="C24" s="21" t="n"/>
       <c r="D24" s="22" t="n"/>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC08</t>
         </is>
@@ -1250,19 +1261,19 @@
       <c r="F24" s="22" t="n"/>
     </row>
     <row r="25" ht="17.25" customHeight="1" s="20">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Overlapping unavailable periods are identifiable.</t>
         </is>
       </c>
       <c r="C25" s="21" t="n"/>
       <c r="D25" s="22" t="n"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC09</t>
         </is>
@@ -1270,19 +1281,19 @@
       <c r="F25" s="22" t="n"/>
     </row>
     <row r="26" ht="30.75" customHeight="1" s="20">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Only authorised internal users can access the availability calendar.</t>
         </is>
       </c>
       <c r="C26" s="21" t="n"/>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC10
 SPM-46-TC11</t>
@@ -1291,19 +1302,19 @@
       <c r="F26" s="22" t="n"/>
     </row>
     <row r="27" ht="44.25" customHeight="1" s="20">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Availability reflects confirmed bookings.</t>
         </is>
       </c>
       <c r="C27" s="21" t="n"/>
       <c r="D27" s="22" t="n"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC12
 SPM-46-TC13
@@ -1314,12 +1325,12 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" s="20"/>
     <row r="29" ht="125.25" customHeight="1" s="20">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>src/app/api/venues/[id]/availability/route.ts
 src/lib/venueAvailability.ts
@@ -2385,7 +2396,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC13</t>
         </is>
@@ -2397,7 +2408,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Changi Conference Centre (CBP-CONF) has a PENDING booking request, 'Pearl Delta Safety Conference', on 14 Dec 2026 and no approved booking that day. Marina Auditorium (MAR-AUD) has a REJECTED booking for 'Nusantara Developer Summit' on 1 Nov 2026. Changi Meeting Room 2 (CBP-MTG2) has a CANCELLED booking for 'Pearl Delta Supplier Forum' on 29 Oct 2026.
@@ -2411,7 +2422,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. Open the availability page for Changi Conference Centre for 14 Dec 2026
 2. Choose Marina Auditorium from the 'Venue' picker and show 1 Nov 2026
@@ -2425,7 +2436,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Changi Conference Centre (CBP-CONF): 14 Dec 2026
 Marina Auditorium (MAR-AUD): 1 Nov 2026
@@ -2439,7 +2450,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.
 On 14 Dec 2026 the Changi Conference Centre slots additionally carry the note 'Requested: Pearl Delta Safety Conference', and a card 'Requested, not yet approved' lists it below the grid. The slots stay 'Free' — a request is not a commitment — but the hold is visible so a second coordinator does not request the same room unaware. The rejected and cancelled bookings carry no such note: they are not live requests.</t>
@@ -2452,7 +2463,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -2484,7 +2495,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.
 On 14 Dec 2026 the Changi Conference Centre slots additionally carry the note 'Requested: Pearl Delta Safety Conference', and a card 'Requested, not yet approved' lists it below the grid. The slots stay 'Free' — a request is not a commitment — but the hold is visible so a second coordinator does not request the same room unaware. The rejected and cancelled bookings carry no such note: they are not live requests.</t>
@@ -2553,7 +2564,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>On all three days every slot shows 'Free'. None of 'Pearl Delta Safety Conference', 'Nusantara Developer Summit' or 'Pearl Delta Supplier Forum' appears under 'Approved bookings' — only an approved booking takes a room.
 On 14 Dec 2026 the Changi Conference Centre slots additionally carry the note 'Requested: Pearl Delta Safety Conference', and a card 'Requested, not yet approved' lists it below the grid. The slots stay 'Free' — a request is not a commitment — but the hold is visible so a second coordinator does not request the same room unaware. The rejected and cancelled bookings carry no such note: they are not live requests.</t>
@@ -3626,7 +3637,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC14</t>
         </is>
@@ -3638,7 +3649,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Jurong Skills Lab (JUR-LAB) is active and has no bookings.
@@ -3652,7 +3663,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. Open Jurong Skills Lab from the Venues list
 2. Click 'Retire venue', then 'Retire venue' in the confirmation dialog
@@ -3668,7 +3679,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Venue: Jurong Skills Lab (JUR-LAB)
 From: 7 Dec 2026
@@ -3682,7 +3693,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>The availability page shows the warning 'This venue is retired'. Every slot on every day shows 'Closed' — none shows 'Free'. After 'Restore venue' the venue is active again.</t>
         </is>
@@ -3694,7 +3705,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -3726,7 +3737,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>The availability page shows the warning 'This venue is retired'. Every slot on every day shows 'Closed' — none shows 'Free'. After 'Restore venue' the venue is active again.</t>
         </is>
@@ -3794,7 +3805,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>The availability page shows the warning 'This venue is retired. It is no longer offered for new bookings, so no slot is shown as free. Anything already booked here is still listed below.'. Every slot on every day shows 'Closed' — none shows 'Free'. After 'Restore venue' the venue is active again.</t>
         </is>
@@ -4859,7 +4870,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC05</t>
         </is>
@@ -4871,7 +4882,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 One-North Auditorium (ONE-AUD) records setup and teardown time, and has an approved booking, 'Bayu Energy Transition Panel', 18:00–21:00 on 9 Nov 2026.
@@ -4885,7 +4896,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Open the availability page for One-North Auditorium
 2. Set 'From' to 9 Nov 2026 and 'To' to 10 Nov 2026
@@ -4899,7 +4910,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Venue: One-North Auditorium (ONE-AUD)
 From: 9 Nov 2026
@@ -4913,7 +4924,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>On 9 Nov 2026: AM shows 'Free'. PM shows 'Turnaround' — the whole slot before the event is taken for setup. Night shows 'Booked' with 'Bayu Energy Transition Panel'. On 10 Nov 2026: AM shows 'Turnaround' — the turnaround runs into the NEXT DAY, because Night is the last slot of its own day; PM and Night show 'Free'. Under 'Approved bookings' the booking shows 18:00–21:00 with 'Room in use' running from 9 Nov 2026, 13:00 to 10 Nov 2026, 12:00 — whole slots, not the recorded minutes.</t>
         </is>
@@ -4925,7 +4936,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -4957,7 +4968,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>On 9 Nov 2026: AM shows 'Free'. PM shows 'Turnaround' — the whole slot before the event is taken for setup. Night shows 'Booked' with 'Bayu Energy Transition Panel'. On 10 Nov 2026: AM shows 'Turnaround' — the turnaround runs into the NEXT DAY, because Night is the last slot of its own day; PM and Night show 'Free'. Under 'Approved bookings' the booking shows 18:00–21:00 with 'Room in use' running from 9 Nov 2026, 13:00 to 10 Nov 2026, 12:00 — whole slots, not the recorded minutes.</t>
         </is>
@@ -5025,7 +5036,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>On 9 Nov 2026: AM shows 'Free'. PM shows 'Turnaround' — the whole slot before the event is taken for setup. Night shows 'Booked' with 'Bayu Energy Transition Panel'. On 10 Nov 2026: AM shows 'Turnaround' — the turnaround runs into the NEXT DAY, because Night is the last slot of its own day; PM and Night show 'Free'. Under 'Approved bookings' the booking shows 18:00–21:00 with 'Room in use' running from 9 Nov 2026, 13:00 to 10 Nov 2026, 12:00 — whole slots, not the recorded minutes.</t>
         </is>
@@ -6088,7 +6099,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC06</t>
         </is>
@@ -6100,7 +6111,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Jurong Expo Floor (JUR-EXP) records setup and teardown time, and has an approved booking, 'Sundara Hospitality Trade Showcase', 10:00–18:00 on 30 Nov 2026.
@@ -6114,7 +6125,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Open the availability page for Jurong Expo Floor
 2. Set 'From' to 29 Nov 2026 and 'To' to 30 Nov 2026
@@ -6128,7 +6139,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
 From: 29 Nov 2026
@@ -6142,7 +6153,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>On 29 Nov 2026: AM and PM show 'Free', and Night shows 'Turnaround' — the event is in the morning, so the slot before it is the PREVIOUS DAY'S Night. On 30 Nov 2026: AM and PM show 'Booked' with 'Sundara Hospitality Trade Showcase' (the event runs 10:00–18:00, and a slot touched at all is taken in full), and Night shows 'Turnaround'. Under 'Approved bookings', 'Room in use' runs from 29 Nov 2026, 19:00 to 1 Dec 2026, 00:00.</t>
         </is>
@@ -6154,7 +6165,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -6186,7 +6197,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>On 29 Nov 2026: AM and PM show 'Free', and Night shows 'Turnaround' — the event is in the morning, so the slot before it is the PREVIOUS DAY'S Night. On 30 Nov 2026: AM and PM show 'Booked' with 'Sundara Hospitality Trade Showcase' (the event runs 10:00–18:00, and a slot touched at all is taken in full), and Night shows 'Turnaround'. Under 'Approved bookings', 'Room in use' runs from 29 Nov 2026, 19:00 to 1 Dec 2026, 00:00.</t>
         </is>
@@ -6254,7 +6265,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>On 29 Nov 2026: AM and PM show 'Free', and Night shows 'Turnaround' — the event is in the morning, so the slot before it is the PREVIOUS DAY'S Night. On 30 Nov 2026: AM and PM show 'Booked' with 'Sundara Hospitality Trade Showcase' (the event runs 10:00–18:00, and a slot touched at all is taken in full), and Night shows 'Turnaround'. Under 'Approved bookings', 'Room in use' runs from 29 Nov 2026, 19:00 to 1 Dec 2026, 00:00.</t>
         </is>
@@ -7317,7 +7328,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC07</t>
         </is>
@@ -7329,7 +7340,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 One-North Rooftop Terrace (ONE-ROOF) is open 16:00–23:00 only, and has no bookings on this date.
@@ -7343,7 +7354,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Open the availability page for One-North Rooftop Terrace
 2. Set 'From' and 'To' to 11 Oct 2026
@@ -7357,7 +7368,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Venue: One-North Rooftop Terrace (ONE-ROOF)
 From: 11 Oct 2026
@@ -7371,7 +7382,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>AM shows 'Closed' — the terrace is shut for the whole of 07:00–12:00. PM shows 'Free' with the note 'Open from 16:00' — only 16:00–18:00 of that slot is bookable. Night shows 'Free' with the note 'Open until 23:00' — the slot runs to midnight but the terrace closes at 23:00.</t>
         </is>
@@ -7383,7 +7394,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -7415,7 +7426,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>AM shows 'Closed' — the terrace is shut for the whole of 07:00–12:00. PM shows 'Free' with the note 'Open from 16:00' — only 16:00–18:00 of that slot is bookable. Night shows 'Free' with the note 'Open until 23:00' — the slot runs to midnight but the terrace closes at 23:00.</t>
         </is>
@@ -7483,7 +7494,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>AM shows 'Closed' — the terrace is shut for the whole of 07:00–12:00. PM shows 'Free' with the note 'Open from 16:00' — only 16:00–18:00 of that slot is bookable. Night shows 'Free' with the note 'Open until 23:00' — the slot runs to midnight but the terrace closes at 23:00.</t>
         </is>
@@ -8546,7 +8557,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC08</t>
         </is>
@@ -8558,7 +8569,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Jurong Expo Floor (JUR-EXP) is recorded as unavailable for renovation from 17 Oct 2026, 00:00 to 24 Oct 2026, 23:59, and has nothing else from 16 to 25 Oct 2026. It is open 06:00–23:00.
@@ -8572,7 +8583,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Open the availability page for Jurong Expo Floor
 2. Set 'From' to 16 Oct 2026 and 'To' to 25 Oct 2026
@@ -8587,7 +8598,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
 From: 16 Oct 2026
@@ -8601,7 +8612,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>16 Oct 2026: AM, PM and Night all show 'Free' (Night with the note 'Open until 23:00') — the period does not start early. 17 to 24 Oct 2026: every slot shows 'Unavailable' — 24 cells, none of them 'Free'. 25 Oct 2026: AM, PM and Night all show 'Free' again — the period stops on its last day and does not spill into the next. Under 'Unavailable periods' exactly one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026, with no 'Overlaps with' note and no overlap warning above the grid.</t>
         </is>
@@ -8613,7 +8624,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -8645,7 +8656,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>16 Oct 2026: AM, PM and Night all show 'Free' (Night with the note 'Open until 23:00') — the period does not start early. 17 to 24 Oct 2026: every slot shows 'Unavailable' — 24 cells, none of them 'Free'. 25 Oct 2026: AM, PM and Night all show 'Free' again — the period stops on its last day and does not spill into the next. Under 'Unavailable periods' exactly one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026, with no 'Overlaps with' note and no overlap warning above the grid.</t>
         </is>
@@ -8713,7 +8724,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>16 Oct 2026: AM, PM and Night all show 'Free' (Night with the note 'Open until 23:00') — the period does not start early. 17 to 24 Oct 2026: every slot shows 'Unavailable' — 24 cells, none of them 'Free'. 25 Oct 2026: AM, PM and Night all show 'Free' again — the period stops on its last day and does not spill into the next. Under 'Unavailable periods' exactly one period is listed: 'Renovation', 'Floor resurfacing and loading bay works.', 17 Oct 2026 to 24 Oct 2026, with no 'Overlaps with' note and no overlap warning above the grid.</t>
         </is>
@@ -9783,7 +9794,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC01</t>
         </is>
@@ -9795,7 +9806,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123</t>
@@ -9808,7 +9819,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. On the 'Marina Grand Hall' row, click 'View availability'
@@ -9826,7 +9837,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Venue: Marina Grand Hall (MAR-GH), then Jurong Expo Floor (JUR-EXP)
 From: 7 Dec 2026
@@ -9840,7 +9851,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>The 'Marina Grand Hall availability' page opens on a week from today (Singapore time): seven day rows, with 'From' and 'To' already filled in with those two dates. The grid has exactly three columns, in this order, each showing its times: AM 07:00–12:00, PM 13:00–18:00, Night 19:00–24:00. After 'Show availability' the grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026 (the 7 Dec row is not empty — it carries the Straits Medical Research Symposium booking). Choosing Jurong Expo Floor changes the title to 'Jurong Expo Floor availability', keeps the range at 7–13 Dec 2026, and shows the same three columns.</t>
         </is>
@@ -9852,7 +9863,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -9884,7 +9895,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>The 'Marina Grand Hall availability' page opens on a week from today (Singapore time): seven day rows, with 'From' and 'To' already filled in with those two dates. The grid has exactly three columns, in this order, each showing its times: AM 07:00–12:00, PM 13:00–18:00, Night 19:00–24:00. After 'Show availability' the grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026 (the 7 Dec row is not empty — it carries the Straits Medical Research Symposium booking). Choosing Jurong Expo Floor changes the title to 'Jurong Expo Floor availability', keeps the range at 7–13 Dec 2026, and shows the same three columns.</t>
         </is>
@@ -9952,7 +9963,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>The 'Marina Grand Hall availability' page opens on a week from today (Singapore time): seven day rows, with 'From' and 'To' already filled in with those two dates. The grid has exactly three columns, in this order, each showing its times: AM 07:00–12:00, PM 13:00–18:00, Night 19:00–24:00. After 'Show availability' the grid shows exactly seven day rows, 7 Dec 2026 to 13 Dec 2026 (the 7 Dec row is not empty — it carries the Straits Medical Research Symposium booking for the AM and PM slot and turnaround for Night slot). Choosing Jurong Expo Floor changes the title to 'Jurong Expo Floor availability', keeps the range at 7–13 Dec 2026, and shows the same three columns.</t>
         </is>
@@ -11017,7 +11028,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC02</t>
         </is>
@@ -11029,7 +11040,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff: marcus.wong@connectsphere.com / password123
 Viewing Marina Grand Hall's availability.</t>
@@ -11042,7 +11053,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Set 'From' to 11 Oct 2026
 2. Set 'To' to 7 Oct 2026
@@ -11056,7 +11067,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>From: 11 Oct 2026
 To: 7 Oct 2026</t>
@@ -11069,7 +11080,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>The message 'The end date must be on or after the start date.' is shown, and no grid is shown for the invalid range.</t>
         </is>
@@ -11081,7 +11092,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -11113,7 +11124,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>The message 'The end date must be on or after the start date.' is shown, and no grid is shown for the invalid range.</t>
         </is>
@@ -11181,7 +11192,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>The message 'The end date must be on or after the start date.' is shown, and no grid is shown for the invalid range.</t>
         </is>
@@ -12244,7 +12255,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC03</t>
         </is>
@@ -12256,7 +12267,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Logged in as Venue Staff: marcus.wong@connectsphere.com / password123
 Viewing Marina Grand Hall's availability.</t>
@@ -12269,7 +12280,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Set 'From' to 7 Oct 2026 and 'To' to 7 Dec 2026
 2. Click 'Show availability'
@@ -12284,7 +12295,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>From: 7 Oct 2026
 62 days — To: 7 Dec 2026
@@ -12298,7 +12309,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>With To = 7 Dec 2026 the grid shows 62 day rows, 7 Oct to 7 Dec 2026. With To = 8 Dec 2026 the message 'Choose a range of 62 days or fewer - this one is 63.' is shown and no grid is shown.</t>
         </is>
@@ -12310,7 +12321,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -12342,7 +12353,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>With To = 7 Dec 2026 the grid shows 62 day rows, 7 Oct to 7 Dec 2026. With To = 8 Dec 2026 the message 'Choose a range of 62 days or fewer - this one is 63.' is shown and no grid is shown.</t>
         </is>
@@ -12410,7 +12421,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>With To = 7 Dec 2026 the grid shows 62 day rows, 7 Oct to 7 Dec 2026. With To = 8 Dec 2026 the message 'Choose a range of 62 days or fewer - this one is 63.' is shown and no grid is shown.</t>
         </is>
@@ -13473,7 +13484,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC04</t>
         </is>
@@ -13485,7 +13496,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Logged in as Venue Staff: marcus.wong@connectsphere.com / password123
@@ -13499,7 +13510,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Click 'Next week'
 2. Click 'Previous week' twice</t>
@@ -13512,7 +13523,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Starting range: 7 Dec 2026 – 13 Dec 2026</t>
         </is>
@@ -13524,7 +13535,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>After 'Next week' the grid shows 14–20 Dec 2026, and the 20 Dec row shows the 'Meridian Wealth Management Forum' booking. After 'Previous week' twice the grid shows 30 Nov 2026 to 6 Dec 2026.</t>
         </is>
@@ -13536,7 +13547,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -13568,7 +13579,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>After 'Next week' the grid shows 14–20 Dec 2026, and the 20 Dec row shows the 'Meridian Wealth Management Forum' booking. After 'Previous week' twice the grid shows 30 Nov 2026 to 6 Dec 2026.</t>
         </is>
@@ -13636,7 +13647,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>After 'Next week' the grid shows 14–20 Dec 2026, and the 20 Dec row shows the 'Meridian Wealth Management Forum' booking. After 'Previous week' twice the grid shows 30 Nov 2026 to 6 Dec 2026.</t>
         </is>
@@ -14706,7 +14717,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC09</t>
         </is>
@@ -14718,7 +14729,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Jurong Expo Floor (JUR-EXP) has TWO unavailable periods that overlap each other: 'Loading bay hoist inspection.' (maintenance) 5–9 Nov 2026, and 'Fire suppression system recertification.' (safety) 7–11 Nov 2026. They are the only overlapping pair in the demo data — nothing in the app can create one until the Block venue screen (S-23) is built, so they are seeded. If they are missing from the shared database, run: npx tsx prisma/topup-spm40-46.ts (adds them without a reseed).
@@ -14732,7 +14743,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. Open the availability page for Jurong Expo Floor
 2. Set 'From' to 5 Nov 2026 and 'To' to 11 Nov 2026
@@ -14747,7 +14758,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Venue: Jurong Expo Floor (JUR-EXP)
 From: 5 Nov 2026
@@ -14761,7 +14772,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid. Under 'Unavailable periods' both are listed — 'Maintenance', 'Loading bay hoist inspection.' and 'Safety', 'Fire suppression system recertification.' — and EACH carries an 'Overlaps with' note naming the other. Every slot from 5 to 11 Nov 2026 shows 'Unavailable', since between them the two periods cover the whole range.</t>
         </is>
@@ -14773,7 +14784,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -14805,7 +14816,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid. Under 'Unavailable periods' both are listed — 'Maintenance', 'Loading bay hoist inspection.' and 'Safety', 'Fire suppression system recertification.' — and EACH carries an 'Overlaps with' note naming the other. Every slot from 5 to 11 Nov 2026 shows 'Unavailable', since between them the two periods cover the whole range.</t>
         </is>
@@ -14873,7 +14884,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A warning 'Some bookings or unavailable periods overlap' is shown above the grid. Under 'Unavailable periods' both are listed — 'Maintenance', 'Loading bay hoist inspection.' and 'Safety', 'Fire suppression system recertification.' — and EACH carries an 'Overlaps with' note naming the other. Every slot from 5 to 11 Nov 2026 shows 'Unavailable', since between them the two periods cover the whole range.</t>
         </is>
@@ -15916,7 +15927,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="20" min="1" max="1"/>
@@ -15924,45 +15935,52 @@
     <col width="12.63" customWidth="1" style="20" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="20">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="20">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="20">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="20">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-46-TC10</t>
-        </is>
-      </c>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="20">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>SPM-46-TC10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84.75" customHeight="1" s="20">
       <c r="A4" s="6" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Logged in as Event Coordinator: daniel.tan@connectsphere.com / password123</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="20">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. Click 'Venues' in the sidebar
 2. On the 'Marina Grand Hall' row, click 'View availability'
@@ -15971,190 +15989,189 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44.25" customHeight="1" s="20">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="6" ht="71.25" customHeight="1" s="20">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Accounts: daniel.tan@connectsphere.com (Event Coordinator), grace.lim@connectsphere.com (Operations Manager)
 Venue: Marina Grand Hall (MAR-GH)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="71.25" customHeight="1" s="20">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
-        </is>
-      </c>
-    </row>
     <row r="7" ht="17.25" customHeight="1" s="20">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>kayalvizhi24</t>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="20">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>kayalvizhi24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="20">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B9" s="16" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="20"/>
-    <row r="10" ht="15.75" customHeight="1" s="20">
-      <c r="A10" s="19" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="20"/>
+    <row r="11" ht="15.75" customHeight="1" s="20">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="20">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
-        </is>
-      </c>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="20">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="20">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="20">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Kayal</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="20">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Kayal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="20">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46291</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="20"/>
     <row r="17" ht="15.75" customHeight="1" s="20"/>
-    <row r="18" ht="15.75" customHeight="1" s="20">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="20"/>
+    <row r="19" ht="15.75" customHeight="1" s="20">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="20">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
-        </is>
-      </c>
+      <c r="B19" s="12" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>Both accounts have 'Venues' in the sidebar, and for both the 'Marina Grand Hall availability' page opens and shows the grid. Clicking elsewhere on the row does nothing — the Venues list stays read-only for both, because neither holds the permission that makes a row editable.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="20">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="20">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Janelle</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="20">
       <c r="A23" s="15" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="20">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B24" s="16" t="n">
         <v>46293</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="20"/>
     <row r="25" ht="15.75" customHeight="1" s="20"/>
     <row r="26" ht="15.75" customHeight="1" s="20"/>
     <row r="27" ht="15.75" customHeight="1" s="20"/>
@@ -17132,6 +17149,9 @@
     <row r="999" ht="15.75" customHeight="1" s="20"/>
     <row r="1000" ht="15.75" customHeight="1" s="20"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -17165,7 +17185,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC11</t>
         </is>
@@ -17177,7 +17197,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>The tester knows the availability page address for Marina Grand Hall.
 Accounts available: rachel.ng@meridianfina.com (Event Organiser) and kenji.sato@connectsphere.com (Technical Support), both / password123</t>
@@ -17190,7 +17210,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1. Sign in as the Event Organiser
 2. Confirm there is no 'Venues' item in the sidebar
@@ -17207,7 +17227,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Account: rachel.ng@meridianfina.com (Event Organiser)
 Account: kenji.sato@connectsphere.com (Technical Support)</t>
@@ -17220,7 +17240,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Neither account has 'Venues' in the sidebar, so neither can reach the calendar by navigating — an Event Organiser sees Dashboard, My Events and Notifications; Technical Support sees Dashboard, Equipment, Equipment Requests and Notifications.
 Typing the address directly is refused as well: the page shows 'Venue availability is for ConnectSphere staff', with no grid, no bookings and no unavailable periods. Hiding the link is not the control — the server refuses it too. Technical Support is internal staff and still has no access, because the calendar reuses the venue catalogue's permission, which they do not hold.</t>
@@ -17233,7 +17253,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -17265,7 +17285,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Neither account has 'Venues' in the sidebar, so neither can reach the calendar by navigating — an Event Organiser sees Dashboard, My Events and Notifications; Technical Support sees Dashboard, Equipment, Equipment Requests and Notifications.
 Typing the address directly is refused as well: the page shows 'Venue availability is for ConnectSphere staff', with no grid, no bookings and no unavailable periods. Hiding the link is not the control — the server refuses it too. Technical Support is internal staff and still has no access, because the calendar reuses the venue catalogue's permission, which they do not hold.</t>
@@ -17334,7 +17354,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Neither account has 'Venues' in the sidebar, so neither can reach the calendar by navigating — an Event Organiser sees Dashboard, My Events and Notifications; Technical Support sees Dashboard, Equipment, Equipment Requests and Notifications.
 Typing the address directly is refused as well: the page shows 'You do not have access to this. Venue availability is for ConnectSphere staff', with no grid, no bookings and no unavailable periods. Hiding the link is not the control — the server refuses it too. Technical Support is internal staff and still has no access, because the calendar reuses the venue catalogue's permission, which they do not hold.</t>
@@ -18405,7 +18425,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>SPM-46-TC12</t>
         </is>
@@ -18417,7 +18437,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Demo data from prisma/seed.ts. Its dates are fixed (2026-09-26 + n days), so a reseed does not move them.
 Marina Grand Hall (MAR-GH) has an APPROVED booking, 'Straits Medical Research Symposium', 09:00–18:00 on 7 Dec 2026, whose EVENT is still in Planning — not Confirmed. The venue has a 180-minute setup and 120-minute teardown.
@@ -18431,7 +18451,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. Open the availability page for Marina Grand Hall
 2. Set 'From' to 6 Dec 2026 and 'To' to 7 Dec 2026
@@ -18446,7 +18466,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Venue: Marina Grand Hall (MAR-GH)
 From: 6 Dec 2026
@@ -18460,7 +18480,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>On 7 Dec 2026 AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free' — and Night shows 'Turnaround'. On 6 Dec 2026 Night shows 'Turnaround' too, for the setup slot before the event. Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use' from 6 Dec 2026, 19:00 to 8 Dec 2026, 00:00. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
         </is>
@@ -18472,7 +18492,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>kayalvizhi24</t>
         </is>
@@ -18504,7 +18524,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>On 7 Dec 2026 AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free' — and Night shows 'Turnaround'. On 6 Dec 2026 Night shows 'Turnaround' too, for the setup slot before the event. Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use' from 6 Dec 2026, 19:00 to 8 Dec 2026, 00:00. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
         </is>
@@ -18572,7 +18592,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>On 7 Dec 2026 AM and PM show 'Booked' with 'Straits Medical Research Symposium' — NOT 'Free' — and Night shows 'Turnaround'. On 6 Dec 2026 Night shows 'Turnaround' too, for the setup slot before the event. Under 'Approved bookings' the booking is listed with the event status 'Planning', 7 Dec 2026, 09:00–18:00, layout 'Theatre', and 'Room in use' from 6 Dec 2026, 19:00 to 8 Dec 2026, 00:00. The room must not read as free: an approved booking already commits it, however far its event has got.</t>
         </is>
